--- a/collateral/SimReal-海外VC名单.xlsx
+++ b/collateral/SimReal-海外VC名单.xlsx
@@ -609,7 +609,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Your State of AI Report tracks the shift to RL post-training, and Air Street backs AI-first companies from seed; SimReal builds the RL environments and verifiers that shift runs on, starting with finance.</t>
+          <t>Your State of AI Report tracks the shift to RL post-training, and Air Street backs AI-first companies from seed; we're building for that shift, starting with finance.</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -639,19 +639,16 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>SimReal: RL environments where AI learns from real outcomes (seed)</t>
+          <t>SimReal: RL environments for finance, built by ex-Jane Street and Citadel quants (seed)</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
           <t>Hi Nathan,
-I'm [Your name], co-founder of SimReal (simreal.co). We build the environments where AI does real work, is scored by real outcomes, and trains on those outcomes.
-Your State of AI Report tracks the shift to RL post-training, and Air Street backs AI-first companies from seed; SimReal builds the RL environments and verifiers that shift runs on, starting with finance.
-- Team: four quants from Cambridge, LSE and Duke, with backgrounds at Jane Street, Citadel, D. E. Shaw, Millennium and Optiver. All four turned down return offers.
-- Proof: our trading environment, Xitadel, improved Qwen3.8-27B's trading performance by 12% on unseen market data, reproduced across independent runs. On its public preview the best frontier model scores 77.3 against a human reference of 80.
-- Speed: seven products in our first 14 days with no outside capital; 500+ GitHub stars in week one.
-- Commercial: in talks with two frontier labs; already working with Surge AI and AfterQuery; 7,000+ experts signed up and 200,000+ professionals reachable through 21 partner universities.
-We're raising a $20M seed and are in conversations with tier-1 funds. Can I send you the deck, or find 30 minutes next week?
+I'm [Your name], co-founder of SimReal (simreal.co). We build RL environments and verifiers where models do real work and are scored on real outcomes.
+Your State of AI Report tracks the shift to RL post-training, and Air Street backs AI-first companies from seed; we're building for that shift, starting with finance.
+Our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke), raising a $20M seed and in conversations with tier-1 funds.
+Worth 20 minutes? Happy to send the deck.
 Best,
 [Your name]
 Co-founder, SimReal
@@ -740,19 +737,16 @@
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>SimReal: RL environments where AI learns from real outcomes (seed)</t>
+          <t>SimReal: RL environments for finance, built by ex-Jane Street and Citadel quants (seed)</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
           <t>Hi Sarah,
-I'm [Your name], co-founder of SimReal (simreal.co). We build the environments where AI does real work, is scored by real outcomes, and trains on those outcomes.
+I'm [Your name], co-founder of SimReal (simreal.co). We build RL environments and verifiers where models do real work and are scored on real outcomes.
 Conviction led Trajectory's seed for continual learning in May; we build the finance environments where that kind of learning gets scored against real outcomes.
-- Team: four quants from Cambridge, LSE and Duke, with backgrounds at Jane Street, Citadel, D. E. Shaw, Millennium and Optiver. All four turned down return offers.
-- Proof: our trading environment, Xitadel, improved Qwen3.8-27B's trading performance by 12% on unseen market data, reproduced across independent runs. On its public preview the best frontier model scores 77.3 against a human reference of 80.
-- Speed: seven products in our first 14 days with no outside capital; 500+ GitHub stars in week one.
-- Commercial: in talks with two frontier labs; already working with Surge AI and AfterQuery; 7,000+ experts signed up and 200,000+ professionals reachable through 21 partner universities.
-We're raising a $20M seed and are in conversations with tier-1 funds. Can I send you the deck, or find 30 minutes next week?
+Our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke), raising a $20M seed and in conversations with tier-1 funds.
+Worth 20 minutes? Happy to send the deck.
 Best,
 [Your name]
 Co-founder, SimReal
@@ -841,19 +835,16 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>SimReal: RL environments where AI learns from real outcomes (seed)</t>
+          <t>SimReal: RL environments for finance, built by ex-Jane Street and Citadel quants (seed)</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
           <t>Hi Vijay,
-I'm [Your name], co-founder of SimReal (simreal.co). We build the environments where AI does real work, is scored by real outcomes, and trains on those outcomes.
+I'm [Your name], co-founder of SimReal (simreal.co). We build RL environments and verifiers where models do real work and are scored on real outcomes.
 Mayfield backed Bespoke Labs on the view that agents depend on data, environments and evaluation; we build all three for finance, from trading to month-end close.
-- Team: four quants from Cambridge, LSE and Duke, with backgrounds at Jane Street, Citadel, D. E. Shaw, Millennium and Optiver. All four turned down return offers.
-- Proof: our trading environment, Xitadel, improved Qwen3.8-27B's trading performance by 12% on unseen market data, reproduced across independent runs. On its public preview the best frontier model scores 77.3 against a human reference of 80.
-- Speed: seven products in our first 14 days with no outside capital; 500+ GitHub stars in week one.
-- Commercial: in talks with two frontier labs; already working with Surge AI and AfterQuery; 7,000+ experts signed up and 200,000+ professionals reachable through 21 partner universities.
-We're raising a $20M seed and are in conversations with tier-1 funds. Can I send you the deck, or find 30 minutes next week?
+Our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke), raising a $20M seed and in conversations with tier-1 funds.
+Worth 20 minutes? Happy to send the deck.
 Best,
 [Your name]
 Co-founder, SimReal
@@ -942,19 +933,16 @@
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>SimReal: RL environments where AI learns from real outcomes (seed)</t>
+          <t>SimReal: RL environments for finance, built by ex-Jane Street and Citadel quants (seed)</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
           <t>Hi Kanyi,
-I'm [Your name], co-founder of SimReal (simreal.co). We build the environments where AI does real work, is scored by real outcomes, and trains on those outcomes.
+I'm [Your name], co-founder of SimReal (simreal.co). We build RL environments and verifiers where models do real work and are scored on real outcomes.
 Kindred led Scorecard's seed to test AI agents across thousands of simulated scenarios; we build the environments and verifiers that train those agents, starting with finance.
-- Team: four quants from Cambridge, LSE and Duke, with backgrounds at Jane Street, Citadel, D. E. Shaw, Millennium and Optiver. All four turned down return offers.
-- Proof: our trading environment, Xitadel, improved Qwen3.8-27B's trading performance by 12% on unseen market data, reproduced across independent runs. On its public preview the best frontier model scores 77.3 against a human reference of 80.
-- Speed: seven products in our first 14 days with no outside capital; 500+ GitHub stars in week one.
-- Commercial: in talks with two frontier labs; already working with Surge AI and AfterQuery; 7,000+ experts signed up and 200,000+ professionals reachable through 21 partner universities.
-We're raising a $20M seed and are in conversations with tier-1 funds. Can I send you the deck, or find 30 minutes next week?
+Our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke), raising a $20M seed and in conversations with tier-1 funds.
+Worth 20 minutes? Happy to send the deck.
 Best,
 [Your name]
 Co-founder, SimReal
@@ -1043,19 +1031,16 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>SimReal: RL environments where AI learns from real outcomes (seed)</t>
+          <t>SimReal: RL environments for finance, built by ex-Jane Street and Citadel quants (seed)</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
           <t>Hi Lu,
-I'm [Your name], co-founder of SimReal (simreal.co). We build the environments where AI does real work, is scored by real outcomes, and trains on those outcomes.
+I'm [Your name], co-founder of SimReal (simreal.co). We build RL environments and verifiers where models do real work and are scored on real outcomes.
 You led AgileRL's seed calling reinforcement learning the gold standard of AI training; we build the finance environments and verifiers that make RL work outside the lab.
-- Team: four quants from Cambridge, LSE and Duke, with backgrounds at Jane Street, Citadel, D. E. Shaw, Millennium and Optiver. All four turned down return offers.
-- Proof: our trading environment, Xitadel, improved Qwen3.8-27B's trading performance by 12% on unseen market data, reproduced across independent runs. On its public preview the best frontier model scores 77.3 against a human reference of 80.
-- Speed: seven products in our first 14 days with no outside capital; 500+ GitHub stars in week one.
-- Commercial: in talks with two frontier labs; already working with Surge AI and AfterQuery; 7,000+ experts signed up and 200,000+ professionals reachable through 21 partner universities.
-We're raising a $20M seed and are in conversations with tier-1 funds. Can I send you the deck, or find 30 minutes next week?
+Our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke), raising a $20M seed and in conversations with tier-1 funds.
+Worth 20 minutes? Happy to send the deck.
 Best,
 [Your name]
 Co-founder, SimReal
@@ -1144,19 +1129,16 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>SimReal: RL environments where AI learns from real outcomes (seed)</t>
+          <t>SimReal: RL environments for finance, built by ex-Jane Street and Citadel quants (seed)</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
           <t>Hi Andy,
-I'm [Your name], co-founder of SimReal (simreal.co). We build the environments where AI does real work, is scored by real outcomes, and trains on those outcomes.
+I'm [Your name], co-founder of SimReal (simreal.co). We build RL environments and verifiers where models do real work and are scored on real outcomes.
 Laude described backing Arena as turning research-driven evaluation into AI infrastructure; we're doing that for finance, where models are scored by real market outcomes.
-- Team: four quants from Cambridge, LSE and Duke, with backgrounds at Jane Street, Citadel, D. E. Shaw, Millennium and Optiver. All four turned down return offers.
-- Proof: our trading environment, Xitadel, improved Qwen3.8-27B's trading performance by 12% on unseen market data, reproduced across independent runs. On its public preview the best frontier model scores 77.3 against a human reference of 80.
-- Speed: seven products in our first 14 days with no outside capital; 500+ GitHub stars in week one.
-- Commercial: in talks with two frontier labs; already working with Surge AI and AfterQuery; 7,000+ experts signed up and 200,000+ professionals reachable through 21 partner universities.
-We're raising a $20M seed and are in conversations with tier-1 funds. Can I send you the deck, or find 30 minutes next week?
+Our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke), raising a $20M seed and in conversations with tier-1 funds.
+Worth 20 minutes? Happy to send the deck.
 Best,
 [Your name]
 Co-founder, SimReal
@@ -1245,19 +1227,16 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>SimReal: RL environments where AI learns from real outcomes (seed)</t>
+          <t>SimReal: RL environments for finance, built by ex-Jane Street and Citadel quants (seed)</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
           <t>Hi Vivek,
-I'm [Your name], co-founder of SimReal (simreal.co). We build the environments where AI does real work, is scored by real outcomes, and trains on those outcomes.
+I'm [Your name], co-founder of SimReal (simreal.co). We build RL environments and verifiers where models do real work and are scored on real outcomes.
 You co-led Gray Swan's Series A after hearing a chorus of praise from frontier labs; we sell those same labs RL environments and verifiers, starting with finance.
-- Team: four quants from Cambridge, LSE and Duke, with backgrounds at Jane Street, Citadel, D. E. Shaw, Millennium and Optiver. All four turned down return offers.
-- Proof: our trading environment, Xitadel, improved Qwen3.8-27B's trading performance by 12% on unseen market data, reproduced across independent runs. On its public preview the best frontier model scores 77.3 against a human reference of 80.
-- Speed: seven products in our first 14 days with no outside capital; 500+ GitHub stars in week one.
-- Commercial: in talks with two frontier labs; already working with Surge AI and AfterQuery; 7,000+ experts signed up and 200,000+ professionals reachable through 21 partner universities.
-We're raising a $20M seed and are in conversations with tier-1 funds. Can I send you the deck, or find 30 minutes next week?
+Our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke), raising a $20M seed and in conversations with tier-1 funds.
+Worth 20 minutes? Happy to send the deck.
 Best,
 [Your name]
 Co-founder, SimReal
@@ -1346,19 +1325,16 @@
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>SimReal: RL environments where AI learns from real outcomes (seed)</t>
+          <t>SimReal: RL environments for finance, built by ex-Jane Street and Citadel quants (seed)</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
           <t>Hi Deedy,
-I'm [Your name], co-founder of SimReal (simreal.co). We build the environments where AI does real work, is scored by real outcomes, and trains on those outcomes.
+I'm [Your name], co-founder of SimReal (simreal.co). We build RL environments and verifiers where models do real work and are scored on real outcomes.
 Your July map counted 50+ companies selling data and RL environments to labs, with most revenue in four players; we're a finance-specialist entrant with quant founders and our own experts.
-- Team: four quants from Cambridge, LSE and Duke, with backgrounds at Jane Street, Citadel, D. E. Shaw, Millennium and Optiver. All four turned down return offers.
-- Proof: our trading environment, Xitadel, improved Qwen3.8-27B's trading performance by 12% on unseen market data, reproduced across independent runs. On its public preview the best frontier model scores 77.3 against a human reference of 80.
-- Speed: seven products in our first 14 days with no outside capital; 500+ GitHub stars in week one.
-- Commercial: in talks with two frontier labs; already working with Surge AI and AfterQuery; 7,000+ experts signed up and 200,000+ professionals reachable through 21 partner universities.
-We're raising a $20M seed and are in conversations with tier-1 funds. Can I send you the deck, or find 30 minutes next week?
+Our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke), raising a $20M seed and in conversations with tier-1 funds.
+Worth 20 minutes? Happy to send the deck.
 Best,
 [Your name]
 Co-founder, SimReal
@@ -1447,19 +1423,16 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>SimReal: RL environments where AI learns from real outcomes (seed)</t>
+          <t>SimReal: RL environments for finance, built by ex-Jane Street and Citadel quants (seed)</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
           <t>Hi Jeremy,
-I'm [Your name], co-founder of SimReal (simreal.co). We build the environments where AI does real work, is scored by real outcomes, and trains on those outcomes.
+I'm [Your name], co-founder of SimReal (simreal.co). We build RL environments and verifiers where models do real work and are scored on real outcomes.
 The House Fund backed Veris AI's seed for simulated environments that train enterprise agents; we build those environments for finance.
-- Team: four quants from Cambridge, LSE and Duke, with backgrounds at Jane Street, Citadel, D. E. Shaw, Millennium and Optiver. All four turned down return offers.
-- Proof: our trading environment, Xitadel, improved Qwen3.8-27B's trading performance by 12% on unseen market data, reproduced across independent runs. On its public preview the best frontier model scores 77.3 against a human reference of 80.
-- Speed: seven products in our first 14 days with no outside capital; 500+ GitHub stars in week one.
-- Commercial: in talks with two frontier labs; already working with Surge AI and AfterQuery; 7,000+ experts signed up and 200,000+ professionals reachable through 21 partner universities.
-We're raising a $20M seed and are in conversations with tier-1 funds. Can I send you the deck, or find 30 minutes next week?
+Our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke), raising a $20M seed and in conversations with tier-1 funds.
+Worth 20 minutes? Happy to send the deck.
 Best,
 [Your name]
 Co-founder, SimReal
@@ -1548,19 +1521,16 @@
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>SimReal: RL environments where AI learns from real outcomes (seed)</t>
+          <t>SimReal: RL environments for finance, built by ex-Jane Street and Citadel quants (seed)</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
           <t>Hi Chris,
-I'm [Your name], co-founder of SimReal (simreal.co). We build the environments where AI does real work, is scored by real outcomes, and trains on those outcomes.
+I'm [Your name], co-founder of SimReal (simreal.co). We build RL environments and verifiers where models do real work and are scored on real outcomes.
 Your RL environments piece argued verification, not model capability, is what makes automation durable; verifiers are the core of what we build for finance.
-- Team: four quants from Cambridge, LSE and Duke, with backgrounds at Jane Street, Citadel, D. E. Shaw, Millennium and Optiver. All four turned down return offers.
-- Proof: our trading environment, Xitadel, improved Qwen3.8-27B's trading performance by 12% on unseen market data, reproduced across independent runs. On its public preview the best frontier model scores 77.3 against a human reference of 80.
-- Speed: seven products in our first 14 days with no outside capital; 500+ GitHub stars in week one.
-- Commercial: in talks with two frontier labs; already working with Surge AI and AfterQuery; 7,000+ experts signed up and 200,000+ professionals reachable through 21 partner universities.
-We're raising a $20M seed and are in conversations with tier-1 funds. Can I send you the deck, or find 30 minutes next week?
+Our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke), raising a $20M seed and in conversations with tier-1 funds.
+Worth 20 minutes? Happy to send the deck.
 Best,
 [Your name]
 Co-founder, SimReal
@@ -1649,19 +1619,16 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>SimReal: RL environments where AI learns from real outcomes (seed)</t>
+          <t>SimReal: RL environments for finance, built by ex-Jane Street and Citadel quants (seed)</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
           <t>Hi Hadley,
-I'm [Your name], co-founder of SimReal (simreal.co). We build the environments where AI does real work, is scored by real outcomes, and trains on those outcomes.
+I'm [Your name], co-founder of SimReal (simreal.co). We build RL environments and verifiers where models do real work and are scored on real outcomes.
 Eniac joined Origin Lab's seed to turn game worlds into AI training data; we turn financial markets into RL environments for the same labs.
-- Team: four quants from Cambridge, LSE and Duke, with backgrounds at Jane Street, Citadel, D. E. Shaw, Millennium and Optiver. All four turned down return offers.
-- Proof: our trading environment, Xitadel, improved Qwen3.8-27B's trading performance by 12% on unseen market data, reproduced across independent runs. On its public preview the best frontier model scores 77.3 against a human reference of 80.
-- Speed: seven products in our first 14 days with no outside capital; 500+ GitHub stars in week one.
-- Commercial: in talks with two frontier labs; already working with Surge AI and AfterQuery; 7,000+ experts signed up and 200,000+ professionals reachable through 21 partner universities.
-We're raising a $20M seed and are in conversations with tier-1 funds. Can I send you the deck, or find 30 minutes next week?
+Our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke), raising a $20M seed and in conversations with tier-1 funds.
+Worth 20 minutes? Happy to send the deck.
 Best,
 [Your name]
 Co-founder, SimReal
@@ -1750,19 +1717,16 @@
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>SimReal: RL environments where AI learns from real outcomes (seed)</t>
+          <t>SimReal: RL environments for finance, built by ex-Jane Street and Citadel quants (seed)</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
           <t>Hi Grace,
-I'm [Your name], co-founder of SimReal (simreal.co). We build the environments where AI does real work, is scored by real outcomes, and trains on those outcomes.
+I'm [Your name], co-founder of SimReal (simreal.co). We build RL environments and verifiers where models do real work and are scored on real outcomes.
 Lux backed Applied Compute twice as enterprises start training their own models; we supply the RL environments and expert data those runs need, starting with finance and accounting.
-- Team: four quants from Cambridge, LSE and Duke, with backgrounds at Jane Street, Citadel, D. E. Shaw, Millennium and Optiver. All four turned down return offers.
-- Proof: our trading environment, Xitadel, improved Qwen3.8-27B's trading performance by 12% on unseen market data, reproduced across independent runs. On its public preview the best frontier model scores 77.3 against a human reference of 80.
-- Speed: seven products in our first 14 days with no outside capital; 500+ GitHub stars in week one.
-- Commercial: in talks with two frontier labs; already working with Surge AI and AfterQuery; 7,000+ experts signed up and 200,000+ professionals reachable through 21 partner universities.
-We're raising a $20M seed and are in conversations with tier-1 funds. Can I send you the deck, or find 30 minutes next week?
+Our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke), raising a $20M seed and in conversations with tier-1 funds.
+Worth 20 minutes? Happy to send the deck.
 Best,
 [Your name]
 Co-founder, SimReal
@@ -1851,19 +1815,16 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>SimReal: RL environments where AI learns from real outcomes (seed)</t>
+          <t>SimReal: RL environments for finance, built by ex-Jane Street and Citadel quants (seed)</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
           <t>Hi Jared,
-I'm [Your name], co-founder of SimReal (simreal.co). We build the environments where AI does real work, is scored by real outcomes, and trains on those outcomes.
+I'm [Your name], co-founder of SimReal (simreal.co). We build RL environments and verifiers where models do real work and are scored on real outcomes.
 TRV has been hosting AI x Wall Street and AI-agent events for the trading world; we're ex-quants building RL environments that train agents on real market data.
-- Team: four quants from Cambridge, LSE and Duke, with backgrounds at Jane Street, Citadel, D. E. Shaw, Millennium and Optiver. All four turned down return offers.
-- Proof: our trading environment, Xitadel, improved Qwen3.8-27B's trading performance by 12% on unseen market data, reproduced across independent runs. On its public preview the best frontier model scores 77.3 against a human reference of 80.
-- Speed: seven products in our first 14 days with no outside capital; 500+ GitHub stars in week one.
-- Commercial: in talks with two frontier labs; already working with Surge AI and AfterQuery; 7,000+ experts signed up and 200,000+ professionals reachable through 21 partner universities.
-We're raising a $20M seed and are in conversations with tier-1 funds. Can I send you the deck, or find 30 minutes next week?
+Our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke), raising a $20M seed and in conversations with tier-1 funds.
+Worth 20 minutes? Happy to send the deck.
 Best,
 [Your name]
 Co-founder, SimReal
@@ -1952,19 +1913,16 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>SimReal: RL environments where AI learns from real outcomes (seed)</t>
+          <t>SimReal: RL environments for finance, built by ex-Jane Street and Citadel quants (seed)</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
           <t>Hi Yuri,
-I'm [Your name], co-founder of SimReal (simreal.co). We build the environments where AI does real work, is scored by real outcomes, and trains on those outcomes.
+I'm [Your name], co-founder of SimReal (simreal.co). We build RL environments and verifiers where models do real work and are scored on real outcomes.
 You led Arga's seed and argued that repeatable sandboxes matter even more for agents; we've built that for finance, where outcomes settle in real markets.
-- Team: four quants from Cambridge, LSE and Duke, with backgrounds at Jane Street, Citadel, D. E. Shaw, Millennium and Optiver. All four turned down return offers.
-- Proof: our trading environment, Xitadel, improved Qwen3.8-27B's trading performance by 12% on unseen market data, reproduced across independent runs. On its public preview the best frontier model scores 77.3 against a human reference of 80.
-- Speed: seven products in our first 14 days with no outside capital; 500+ GitHub stars in week one.
-- Commercial: in talks with two frontier labs; already working with Surge AI and AfterQuery; 7,000+ experts signed up and 200,000+ professionals reachable through 21 partner universities.
-We're raising a $20M seed and are in conversations with tier-1 funds. Can I send you the deck, or find 30 minutes next week?
+Our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke), raising a $20M seed and in conversations with tier-1 funds.
+Worth 20 minutes? Happy to send the deck.
 Best,
 [Your name]
 Co-founder, SimReal
@@ -2049,19 +2007,16 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>SimReal: RL environments where AI learns from real outcomes (seed)</t>
+          <t>SimReal: RL environments for finance, built by ex-Jane Street and Citadel quants (seed)</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
           <t>Hi HRT Ventures team,
-I'm [Your name], co-founder of SimReal (simreal.co). We build the environments where AI does real work, is scored by real outcomes, and trains on those outcomes.
+I'm [Your name], co-founder of SimReal (simreal.co). We build RL environments and verifiers where models do real work and are scored on real outcomes.
 HRT Ventures joined Vals AI's Series A in August; we build trading RL environments, and our founders come from the same quant world.
-- Team: four quants from Cambridge, LSE and Duke, with backgrounds at Jane Street, Citadel, D. E. Shaw, Millennium and Optiver. All four turned down return offers.
-- Proof: our trading environment, Xitadel, improved Qwen3.8-27B's trading performance by 12% on unseen market data, reproduced across independent runs. On its public preview the best frontier model scores 77.3 against a human reference of 80.
-- Speed: seven products in our first 14 days with no outside capital; 500+ GitHub stars in week one.
-- Commercial: in talks with two frontier labs; already working with Surge AI and AfterQuery; 7,000+ experts signed up and 200,000+ professionals reachable through 21 partner universities.
-We're raising a $20M seed and are in conversations with tier-1 funds. Can I send you the deck, or find 30 minutes next week?
+Our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke), raising a $20M seed and in conversations with tier-1 funds.
+Worth 20 minutes? Happy to send the deck.
 Best,
 [Your name]
 Co-founder, SimReal

--- a/collateral/SimReal-海外VC名单.xlsx
+++ b/collateral/SimReal-海外VC名单.xlsx
@@ -474,7 +474,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>批次</t>
+          <t>分组</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -564,12 +564,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>第 1 批：先发</t>
+          <t>C 组：先发练手</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Air Street Capital</t>
+          <t>The House Fund</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -579,76 +579,77 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>海外（英国，伦敦）</t>
+          <t>海外（美国）</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Nathan Benaich</t>
+          <t>Jeremy Fiance</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>创始人、Solo GP；State of AI Report 作者</t>
+          <t>创始人、Managing Partner</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>nathan@airstreet.com</t>
+          <t>build@thehouse.fund</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>个人公开</t>
+          <t>官方投递</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>直接写给 Nathan Benaich</t>
+          <t>第一句写明请转交 Jeremy Fiance（Could you pass this to Jeremy Fiance?）</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Your State of AI Report tracks the shift to RL post-training, and Air Street backs AI-first companies from seed; we're building for that shift, starting with finance.</t>
+          <t>The House Fund backed Veris AI's seed for simulated environments that train enterprise agents; we build those environments for finance.</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>只投 AI-first 公司，官网写明回复所有可信的创业者来信；创始人剑桥博士，State of AI 报告一直在跟 RL 后训练。</t>
+          <t>C 组（先发练手）：匹配度相对低，用这一组的回复打磨话术。</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>单笔偏小，2,000 万美元种子轮里更可能是参投；官网要求邮件写清公司简介、核心 AI 能力和阶段，本人提过 AI 生成的 pitch 邮件太多，邮件要短而具体</t>
+          <t>只投至少一位创始人与 UC Berkeley 相关的团队，SimReal 团队如无伯克利关联则不符合。</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>https://www.airstreet.com/ai-venture-capital (搜索摘要，官网原文：The best way to reach Air Street Capital is to email Nathan Benaich directly at nathan@airstreet.com)</t>
+          <t>build@thehouse.fund（官网联系页 https://thehouse.fund/contact）</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>https://www.airstreet.com/team (搜索摘要) ; https://www.airstreet.com/ai-venture-capital (搜索摘要)</t>
+          <t>https://thehouse.fund/team (搜索摘要) ; https://pitchbook.com/news/articles/house-fund-raises-12m-fund-berkeley-ai-research (搜索摘要)</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>v-air-street-capital</t>
+          <t>v-the-house-fund</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>SimReal: RL environments for finance, built by ex-Jane Street and Citadel quants (seed)</t>
+          <t>Ex-Jane Street quants building RL environments, supplying Surge AI</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>Hi Nathan,
-I'm [Your name], co-founder of SimReal (simreal.co). We build RL environments and verifiers where models do real work and are scored on real outcomes.
-Your State of AI Report tracks the shift to RL post-training, and Air Street backs AI-first companies from seed; we're building for that shift, starting with finance.
-Our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke), raising a $20M seed and in conversations with tier-1 funds.
-Worth 20 minutes? Happy to send the deck.
+          <t>Hi Jeremy,
+The House Fund backed Veris AI's seed for simulated environments that train enterprise agents; we build those environments for finance.
+I'm [Your name], co-founder of SimReal. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke).
+SimReal builds RL environments and verifiers where AI models do real work and are scored on real outcomes.
+Traction: our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up.
+We're raising a $20M seed and are in conversations with tier-1 funds. Deck: [Deck link]. Worth 20 minutes next week?
 Best,
 [Your name]
 Co-founder, SimReal
@@ -662,12 +663,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>第 1 批：先发</t>
+          <t>B 组</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Conviction</t>
+          <t>Fusion Fund</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -682,71 +683,72 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Sarah Guo</t>
+          <t>Lu Zhang</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>创始人</t>
+          <t>创始人、Managing Partner</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>sarah@conviction.com</t>
+          <t>info@fusionfund.com</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>个人公开</t>
+          <t>官方通用</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>直接写给 Sarah Guo</t>
+          <t>第一句写明请转交 Lu Zhang（Could you pass this to Lu Zhang?）</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Conviction led Trajectory's seed for continual learning in May; we build the finance environments where that kind of learning gets scored against real outcomes.</t>
+          <t>You led AgileRL's seed calling reinforcement learning the gold standard of AI training; we build the finance environments and verifiers that make RL work outside the lab.</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>种子基金，创始人本人关注 agent 持续学习；投过 HeyGen，对华人团队友好。</t>
+          <t>B 组：方向匹配，在 C 组之后发。</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Conviction 主张机会在模型层之上，偏应用；RL 环境直接案例少。</t>
+          <t>AgileRL 为 RL 训练平台，属互补而非竞品。</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>https://x.com/saranormous ; https://www.linkedin.com/posts/sarahxguo_conviction-activity-6972973704561520640-BmeQ (搜索摘要：精确搜索该地址，结果指向本人 X 和本人 LinkedIn 帖子)</t>
+          <t>info@fusionfund.com（官网联系页 https://www.fusionfund.com/contactus）</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>https://www.forbes.com/sites/rashishrivastava/2026/05/27/sarah-guo-bet-everything-on-ai-pre-chatgpt-now-shes-one-of-the-worlds-top-investors/ (搜索摘要) ; https://en.wikipedia.org/wiki/Sarah_Guo (搜索摘要)</t>
+          <t>https://en.wikipedia.org/wiki/Lu_Zhang_(venture_capitalist) (搜索摘要) ; https://aijourn.com/agilerl-raises-7-5m-to-take-reinforcement-learning-out-of-the-research-lab-and-into-the-enterprise/ (搜索摘要)</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>v-conviction</t>
+          <t>v-fusion-fund</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>SimReal: RL environments for finance, built by ex-Jane Street and Citadel quants (seed)</t>
+          <t>Ex-Jane Street quants building RL environments, supplying Surge AI</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>Hi Sarah,
-I'm [Your name], co-founder of SimReal (simreal.co). We build RL environments and verifiers where models do real work and are scored on real outcomes.
-Conviction led Trajectory's seed for continual learning in May; we build the finance environments where that kind of learning gets scored against real outcomes.
-Our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke), raising a $20M seed and in conversations with tier-1 funds.
-Worth 20 minutes? Happy to send the deck.
+          <t>Hi Lu,
+You led AgileRL's seed calling reinforcement learning the gold standard of AI training; we build the finance environments and verifiers that make RL work outside the lab.
+I'm [Your name], co-founder of SimReal. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke).
+SimReal builds RL environments and verifiers where AI models do real work and are scored on real outcomes.
+Traction: our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up.
+We're raising a $20M seed and are in conversations with tier-1 funds. Deck: [Deck link]. Worth 20 minutes next week?
 Best,
 [Your name]
 Co-founder, SimReal
@@ -760,12 +762,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>第 1 批：先发</t>
+          <t>B 组</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Mayfield</t>
+          <t>Madrona</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -775,76 +777,77 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>海外（美国）</t>
+          <t>海外（美国，西雅图）</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Vijay Reddy</t>
+          <t>Vivek Ramaswami</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Partner（AI Start 种子基金）</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>aistart@mayfield.com</t>
+          <t>vivek@madrona.com</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>官方投递</t>
+          <t>个人公开</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>第一句写明请转交 Vijay Reddy（Could you pass this to Vijay Reddy?）</t>
+          <t>直接写给 Vivek Ramaswami</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Mayfield backed Bespoke Labs on the view that agents depend on data, environments and evaluation; we build all three for finance, from trading to month-end close.</t>
+          <t>You co-led Gray Swan's Series A after hearing a chorus of praise from frontier labs; we sell those same labs RL environments and verifiers, starting with finance.</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>投过 RL 环境公司，种子阶段活跃。</t>
+          <t>B 组：方向匹配，在 C 组之后发。 原排序理由：领投过红队/评测，没有 RL 环境竞品；阶段偏 A 轮。</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>已投 Bespoke Labs（RL 环境竞品）；Vijay 是否负责 Bespoke 未证实。</t>
+          <t>阶段偏 A 轮；无 RL 环境直接竞品冲突。</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>aistart@mayfield.com（Mayfield 官网 AI Start 页，搜索摘要 https://www.mayfield.com/ai-start-pathfinders/）</t>
+          <t>https://substack.com/@aspiringforintelligence (搜索摘要：精确搜索该地址，首条结果是本人 Substack)</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>https://www.mayfield.com/team/vijay-reddy/ (搜索摘要) ; https://www.linkedin.com/in/vijayreddy/ (搜索摘要)</t>
+          <t>https://www.madrona.com/team-profiles/vivek-ramaswami/ (搜索摘要) ; https://www.madrona.com/gray-swan-series-a/ (搜索摘要)</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>v-mayfield</t>
+          <t>v-madrona</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>SimReal: RL environments for finance, built by ex-Jane Street and Citadel quants (seed)</t>
+          <t>Ex-Jane Street quants building RL environments, supplying Surge AI</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>Hi Vijay,
-I'm [Your name], co-founder of SimReal (simreal.co). We build RL environments and verifiers where models do real work and are scored on real outcomes.
-Mayfield backed Bespoke Labs on the view that agents depend on data, environments and evaluation; we build all three for finance, from trading to month-end close.
-Our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke), raising a $20M seed and in conversations with tier-1 funds.
-Worth 20 minutes? Happy to send the deck.
+          <t>Hi Vivek,
+You co-led Gray Swan's Series A after hearing a chorus of praise from frontier labs; we sell those same labs RL environments and verifiers, starting with finance.
+I'm [Your name], co-founder of SimReal. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke).
+SimReal builds RL environments and verifiers where AI models do real work and are scored on real outcomes.
+Traction: our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up.
+We're raising a $20M seed and are in conversations with tier-1 funds. Deck: [Deck link]. Worth 20 minutes next week?
 Best,
 [Your name]
 Co-founder, SimReal
@@ -858,12 +861,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>第 1 批：先发</t>
+          <t>B 组</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Kindred Ventures</t>
+          <t>Eniac Ventures</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -878,71 +881,72 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Kanyi Maqubela</t>
+          <t>Hadley Harris</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Managing Partner</t>
+          <t>联合创始人、General Partner（AI 原生、数据基础设施方向）</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>hello@kindredventures.com</t>
+          <t>pitch@eniac.vc</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>官方通用</t>
+          <t>官方投递</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>第一句写明请转交 Kanyi Maqubela（Could you pass this to Kanyi Maqubela?）</t>
+          <t>第一句写明请转交 Hadley Harris（Could you pass this to Hadley Harris?）</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Kindred led Scorecard's seed to test AI agents across thousands of simulated scenarios; we build the environments and verifiers that train those agents, starting with finance.</t>
+          <t>Eniac joined Origin Lab's seed to turn game worlds into AI training data; we turn financial markets into RL environments for the same labs.</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>种子领投过 agent 评测，没有 RL 环境竞品。</t>
+          <t>B 组：方向匹配，在 C 组之后发。</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Scorecard 由哪位合伙人负责未知；无竞品冲突。</t>
+          <t>负责 Origin Lab 的合伙人未确认。</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>hello@kindredventures.com（官网，搜索摘要 https://kindredventures.com/）</t>
+          <t>pitch@eniac.vc（Eniac 官方 Medium 投递说明 https://eniacvc.medium.com/eniac-ventures-is-ready-for-your-pitches-again-27fa23f5e5d8）</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>https://kindredventures.com/about/kanyi-maqubela/ (搜索摘要) ; https://techcrunch.com/2019/11/18/kindred-ventures/ (搜索摘要)</t>
+          <t>https://www.eniac.vc/team (搜索摘要) ; https://signal.nfx.com/investors/hadley-harris (搜索摘要)</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>v-kindred-ventures</t>
+          <t>v-eniac-ventures</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>SimReal: RL environments for finance, built by ex-Jane Street and Citadel quants (seed)</t>
+          <t>Ex-Jane Street quants building RL environments, supplying Surge AI</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>Hi Kanyi,
-I'm [Your name], co-founder of SimReal (simreal.co). We build RL environments and verifiers where models do real work and are scored on real outcomes.
-Kindred led Scorecard's seed to test AI agents across thousands of simulated scenarios; we build the environments and verifiers that train those agents, starting with finance.
-Our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke), raising a $20M seed and in conversations with tier-1 funds.
-Worth 20 minutes? Happy to send the deck.
+          <t>Hi Hadley,
+Eniac joined Origin Lab's seed to turn game worlds into AI training data; we turn financial markets into RL environments for the same labs.
+I'm [Your name], co-founder of SimReal. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke).
+SimReal builds RL environments and verifiers where AI models do real work and are scored on real outcomes.
+Traction: our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up.
+We're raising a $20M seed and are in conversations with tier-1 funds. Deck: [Deck link]. Worth 20 minutes next week?
 Best,
 [Your name]
 Co-founder, SimReal
@@ -956,12 +960,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>B 组</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Fusion Fund</t>
+          <t>Lux Capital</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -976,17 +980,17 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Lu Zhang</t>
+          <t>Grace Isford</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>创始人、Managing Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>info@fusionfund.com</t>
+          <t>info@luxcapital.com</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -996,51 +1000,52 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>第一句写明请转交 Lu Zhang（Could you pass this to Lu Zhang?）</t>
+          <t>第一句写明请转交 Grace Isford（Could you pass this to Grace Isford?）</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>You led AgileRL's seed calling reinforcement learning the gold standard of AI training; we build the finance environments and verifiers that make RL work outside the lab.</t>
+          <t>Lux backed Applied Compute twice as enterprises start training their own models; we supply the RL environments and expert data those runs need, starting with finance and accounting.</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>种子轮领投。</t>
+          <t>B 组：方向匹配，在 C 组之后发。 原排序理由：持续加注后训练平台，没有竞品冲突。</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>AgileRL 为 RL 训练平台，属互补而非竞品。</t>
+          <t>Applied Compute 可能自建环境；Grace 与 Applied Compute 的关系仅见 Lux 公司页列名。</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>info@fusionfund.com（官网联系页 https://www.fusionfund.com/contactus）</t>
+          <t>info@luxcapital.com（官网联系页 https://www.luxcapital.com/contact）</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Lu_Zhang_(venture_capitalist) (搜索摘要) ; https://aijourn.com/agilerl-raises-7-5m-to-take-reinforcement-learning-out-of-the-research-lab-and-into-the-enterprise/ (搜索摘要)</t>
+          <t>https://www.luxcapital.com/people/grace-isford (搜索摘要) ; https://www.luxcapital.com/companies/applied-compute (搜索摘要)</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>v-fusion-fund</t>
+          <t>v-lux-capital</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>SimReal: RL environments for finance, built by ex-Jane Street and Citadel quants (seed)</t>
+          <t>Ex-Jane Street quants building RL environments, supplying Surge AI</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>Hi Lu,
-I'm [Your name], co-founder of SimReal (simreal.co). We build RL environments and verifiers where models do real work and are scored on real outcomes.
-You led AgileRL's seed calling reinforcement learning the gold standard of AI training; we build the finance environments and verifiers that make RL work outside the lab.
-Our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke), raising a $20M seed and in conversations with tier-1 funds.
-Worth 20 minutes? Happy to send the deck.
+          <t>Hi Grace,
+Lux backed Applied Compute twice as enterprises start training their own models; we supply the RL environments and expert data those runs need, starting with finance and accounting.
+I'm [Your name], co-founder of SimReal. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke).
+SimReal builds RL environments and verifiers where AI models do real work and are scored on real outcomes.
+Traction: our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up.
+We're raising a $20M seed and are in conversations with tier-1 funds. Deck: [Deck link]. Worth 20 minutes next week?
 Best,
 [Your name]
 Co-founder, SimReal
@@ -1054,12 +1059,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>B 组</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Laude Ventures</t>
+          <t>Mayfield</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1074,71 +1079,72 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Andy Konwinski</t>
+          <t>Vijay Reddy</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>联合创始人（Laude Ventures / Laude Institute，Databricks、Perplexity 联合创始人）</t>
+          <t>Partner（AI Start 种子基金）</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>hello@laude.vc</t>
+          <t>aistart@mayfield.com</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>官方通用</t>
+          <t>官方投递</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>第一句写明请转交 Andy Konwinski（Could you pass this to Andy Konwinski?）</t>
+          <t>第一句写明请转交 Vijay Reddy（Could you pass this to Vijay Reddy?）</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Laude described backing Arena as turning research-driven evaluation into AI infrastructure; we're doing that for finance, where models are scored by real market outcomes.</t>
+          <t>Mayfield backed Bespoke Labs on the view that agents depend on data, environments and evaluation; we build all three for finance, from trading to month-end close.</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>种子轮投资；Laude Institute 的 Terminal-Bench 等基准资源可合作。</t>
+          <t>B 组：方向匹配，在 C 组之后发。 原排序理由：投过 RL 环境公司，种子阶段活跃。</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>偏好研究出身的技术团队。</t>
+          <t>已投 Bespoke Labs（RL 环境竞品）；Vijay 是否负责 Bespoke 未证实。</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>hello@laude.vc（官方通用；精确搜索该地址，结果指向 laude.vc 官网页面，搜索摘要） ；https://laude.vc（官网联系表单）</t>
+          <t>aistart@mayfield.com（Mayfield 官网 AI Start 页，搜索摘要 https://www.mayfield.com/ai-start-pathfinders/）</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>https://laude.vc/team/andy-konwinski (搜索摘要) ; https://laude.vc/team (搜索摘要)</t>
+          <t>https://www.mayfield.com/team/vijay-reddy/ (搜索摘要) ; https://www.linkedin.com/in/vijayreddy/ (搜索摘要)</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>v-laude-ventures</t>
+          <t>v-mayfield</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>SimReal: RL environments for finance, built by ex-Jane Street and Citadel quants (seed)</t>
+          <t>Ex-Jane Street quants building RL environments, supplying Surge AI</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>Hi Andy,
-I'm [Your name], co-founder of SimReal (simreal.co). We build RL environments and verifiers where models do real work and are scored on real outcomes.
-Laude described backing Arena as turning research-driven evaluation into AI infrastructure; we're doing that for finance, where models are scored by real market outcomes.
-Our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke), raising a $20M seed and in conversations with tier-1 funds.
-Worth 20 minutes? Happy to send the deck.
+          <t>Hi Vijay,
+Mayfield backed Bespoke Labs on the view that agents depend on data, environments and evaluation; we build all three for finance, from trading to month-end close.
+I'm [Your name], co-founder of SimReal. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke).
+SimReal builds RL environments and verifiers where AI models do real work and are scored on real outcomes.
+Traction: our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up.
+We're raising a $20M seed and are in conversations with tier-1 funds. Deck: [Deck link]. Worth 20 minutes next week?
 Best,
 [Your name]
 Co-founder, SimReal
@@ -1152,12 +1158,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>B 组</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Madrona</t>
+          <t>Tower Research Ventures</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1167,76 +1173,77 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>海外（美国，西雅图）</t>
+          <t>海外（美国，纽约）</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Vivek Ramaswami</t>
+          <t>Jared Young</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>Director of Venture Capital</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>vivek@madrona.com</t>
+          <t>ventures@tower-research.com</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>个人公开</t>
+          <t>官方投递</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>直接写给 Vivek Ramaswami</t>
+          <t>第一句写明请转交 Jared Young（Could you pass this to Jared Young?）</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>You co-led Gray Swan's Series A after hearing a chorus of praise from frontier labs; we sell those same labs RL environments and verifiers, starting with finance.</t>
+          <t>TRV has been hosting AI x Wall Street and AI-agent events for the trading world; we're ex-quants building RL environments that train agents on real market data.</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>领投过红队/评测，没有 RL 环境竞品；阶段偏 A 轮。</t>
+          <t>B 组：方向匹配，在 C 组之后发。</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>阶段偏 A 轮；无 RL 环境直接竞品冲突。</t>
+          <t>规模小；投资组合偏应用 AI 与加密。</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>https://substack.com/@aspiringforintelligence (搜索摘要：精确搜索该地址，首条结果是本人 Substack)</t>
+          <t>ventures@tower-research.com（官网 Ventures 页，搜索摘要 https://tower-research.com/ventures/）</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>https://www.madrona.com/team-profiles/vivek-ramaswami/ (搜索摘要) ; https://www.madrona.com/gray-swan-series-a/ (搜索摘要)</t>
+          <t>https://tower-research.com/ventures/ (搜索摘要)</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>v-madrona</t>
+          <t>v-tower-research-ventures</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>SimReal: RL environments for finance, built by ex-Jane Street and Citadel quants (seed)</t>
+          <t>Ex-Jane Street quants building RL environments, supplying Surge AI</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>Hi Vivek,
-I'm [Your name], co-founder of SimReal (simreal.co). We build RL environments and verifiers where models do real work and are scored on real outcomes.
-You co-led Gray Swan's Series A after hearing a chorus of praise from frontier labs; we sell those same labs RL environments and verifiers, starting with finance.
-Our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke), raising a $20M seed and in conversations with tier-1 funds.
-Worth 20 minutes? Happy to send the deck.
+          <t>Hi Jared,
+TRV has been hosting AI x Wall Street and AI-agent events for the trading world; we're ex-quants building RL environments that train agents on real market data.
+I'm [Your name], co-founder of SimReal. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke).
+SimReal builds RL environments and verifiers where AI models do real work and are scored on real outcomes.
+Traction: our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up.
+We're raising a $20M seed and are in conversations with tier-1 funds. Deck: [Deck link]. Worth 20 minutes next week?
 Best,
 [Your name]
 Co-founder, SimReal
@@ -1250,12 +1257,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>B 组</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Menlo Ventures</t>
+          <t>Kindred Ventures</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1270,71 +1277,72 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Deedy Das</t>
+          <t>Kanyi Maqubela</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Partner（种子到 B 轮 AI/基础设施）</t>
+          <t>Managing Partner</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>deedy@menlovc.com</t>
+          <t>hello@kindredventures.com</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>个人公开</t>
+          <t>官方通用</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>直接写给 Deedy Das</t>
+          <t>第一句写明请转交 Kanyi Maqubela（Could you pass this to Kanyi Maqubela?）</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Your July map counted 50+ companies selling data and RL environments to labs, with most revenue in four players; we're a finance-specialist entrant with quant founders and our own experts.</t>
+          <t>Kindred led Scorecard's seed to test AI agents across thousands of simulated scenarios; we build the environments and verifiers that train those agents, starting with finance.</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>对赛道最熟的合伙人之一；但持有 Fleet、Mercor，要讲清差异。</t>
+          <t>B 组：方向匹配，在 C 组之后发。 原排序理由：种子领投过 agent 评测，没有 RL 环境竞品。</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>已投 Fleet、Mercor 两家直接竞品。</t>
+          <t>Scorecard 由哪位合伙人负责未知；无竞品冲突。</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>https://debarghyadas.com/ (搜索摘要：精确搜索该地址，首条结果是本人主页)</t>
+          <t>hello@kindredventures.com（官网，搜索摘要 https://kindredventures.com/）</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://menlovc.com/team/deedy-das/ (搜索摘要) ; https://slush.org/2026-speakers/deedy-das (搜索摘要)</t>
+          <t>https://kindredventures.com/about/kanyi-maqubela/ (搜索摘要) ; https://techcrunch.com/2019/11/18/kindred-ventures/ (搜索摘要)</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>v-menlo-ventures</t>
+          <t>v-kindred-ventures</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>SimReal: RL environments for finance, built by ex-Jane Street and Citadel quants (seed)</t>
+          <t>Ex-Jane Street quants building RL environments, supplying Surge AI</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>Hi Deedy,
-I'm [Your name], co-founder of SimReal (simreal.co). We build RL environments and verifiers where models do real work and are scored on real outcomes.
-Your July map counted 50+ companies selling data and RL environments to labs, with most revenue in four players; we're a finance-specialist entrant with quant founders and our own experts.
-Our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke), raising a $20M seed and in conversations with tier-1 funds.
-Worth 20 minutes? Happy to send the deck.
+          <t>Hi Kanyi,
+Kindred led Scorecard's seed to test AI agents across thousands of simulated scenarios; we build the environments and verifiers that train those agents, starting with finance.
+I'm [Your name], co-founder of SimReal. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke).
+SimReal builds RL environments and verifiers where AI models do real work and are scored on real outcomes.
+Traction: our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up.
+We're raising a $20M seed and are in conversations with tier-1 funds. Deck: [Deck link]. Worth 20 minutes next week?
 Best,
 [Your name]
 Co-founder, SimReal
@@ -1348,12 +1356,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>A 组：最匹配，最后发</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>The House Fund</t>
+          <t>Air Street Capital</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1363,76 +1371,77 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>海外（美国）</t>
+          <t>海外（英国，伦敦）</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Jeremy Fiance</t>
+          <t>Nathan Benaich</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>创始人、Managing Partner</t>
+          <t>创始人、Solo GP；State of AI Report 作者</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>build@thehouse.fund</t>
+          <t>nathan@airstreet.com</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>官方投递</t>
+          <t>个人公开</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>第一句写明请转交 Jeremy Fiance（Could you pass this to Jeremy Fiance?）</t>
+          <t>直接写给 Nathan Benaich</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>The House Fund backed Veris AI's seed for simulated environments that train enterprise agents; we build those environments for finance.</t>
+          <t>Your State of AI Report tracks the shift to RL post-training, and Air Street backs AI-first companies from seed; we're building for that shift, starting with finance.</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>种子轮跟投。</t>
+          <t>A 组（最后发）：最匹配、最想拿下，话术成熟后再发。 原排序理由：只投 AI-first 公司，官网写明回复所有可信的创业者来信；创始人剑桥博士，State of AI 报告一直在跟 RL 后训练。</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>只投至少一位创始人与 UC Berkeley 相关的团队，SimReal 团队如无伯克利关联则不符合。</t>
+          <t>单笔偏小，2,000 万美元种子轮里更可能是参投；官网要求邮件写清公司简介、核心 AI 能力和阶段，本人提过 AI 生成的 pitch 邮件太多，邮件要短而具体</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>build@thehouse.fund（官网联系页 https://thehouse.fund/contact）</t>
+          <t>https://www.airstreet.com/ai-venture-capital (搜索摘要，官网原文：The best way to reach Air Street Capital is to email Nathan Benaich directly at nathan@airstreet.com)</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://thehouse.fund/team (搜索摘要) ; https://pitchbook.com/news/articles/house-fund-raises-12m-fund-berkeley-ai-research (搜索摘要)</t>
+          <t>https://www.airstreet.com/team (搜索摘要) ; https://www.airstreet.com/ai-venture-capital (搜索摘要)</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>v-the-house-fund</t>
+          <t>v-air-street-capital</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>SimReal: RL environments for finance, built by ex-Jane Street and Citadel quants (seed)</t>
+          <t>Ex-Jane Street quants building RL environments, supplying Surge AI</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>Hi Jeremy,
-I'm [Your name], co-founder of SimReal (simreal.co). We build RL environments and verifiers where models do real work and are scored on real outcomes.
-The House Fund backed Veris AI's seed for simulated environments that train enterprise agents; we build those environments for finance.
-Our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke), raising a $20M seed and in conversations with tier-1 funds.
-Worth 20 minutes? Happy to send the deck.
+          <t>Hi Nathan,
+Your State of AI Report tracks the shift to RL post-training, and Air Street backs AI-first companies from seed; we're building for that shift, starting with finance.
+I'm [Your name], co-founder of SimReal. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke).
+SimReal builds RL environments and verifiers where AI models do real work and are scored on real outcomes.
+Traction: our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up.
+We're raising a $20M seed and are in conversations with tier-1 funds. Deck: [Deck link]. Worth 20 minutes next week?
 Best,
 [Your name]
 Co-founder, SimReal
@@ -1446,12 +1455,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>A 组：最匹配，最后发</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Wing VC</t>
+          <t>Conviction</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1466,17 +1475,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Chris Zeoli</t>
+          <t>Sarah Guo</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Partner（数据基础设施/AI 基础设施）</t>
+          <t>创始人</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>chris@wing.vc</t>
+          <t>sarah@conviction.com</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1486,51 +1495,52 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>直接写给 Chris Zeoli</t>
+          <t>直接写给 Sarah Guo</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Your RL environments piece argued verification, not model capability, is what makes automation durable; verifiers are the core of what we build for finance.</t>
+          <t>Conviction led Trajectory's seed for continual learning in May; we build the finance environments where that kind of learning gets scored against real outcomes.</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>写过 RL 环境市场研究，强调验证，正对我们的卖点；但持有 Bespoke，偏 A 轮。</t>
+          <t>A 组（最后发）：最匹配、最想拿下，话术成熟后再发。 原排序理由：种子基金，创始人本人关注 agent 持续学习；投过 HeyGen，对华人团队友好。</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>已投 Bespoke Labs（RL 环境），偏 A 轮。</t>
+          <t>Conviction 主张机会在模型层之上，偏应用；RL 环境直接案例少。</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>https://x.com/chriszeoli ; https://www.wing.vc/team (搜索摘要：本人公开写法为 "Chris [at] wing.vc"，精确搜索结果指向本人 X 和 Wing 团队页)</t>
+          <t>https://x.com/saranormous ; https://www.linkedin.com/posts/sarahxguo_conviction-activity-6972973704561520640-BmeQ (搜索摘要：精确搜索该地址，结果指向本人 X 和本人 LinkedIn 帖子)</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>https://www.wing.vc/people/chris-zeoli (搜索摘要)</t>
+          <t>https://www.forbes.com/sites/rashishrivastava/2026/05/27/sarah-guo-bet-everything-on-ai-pre-chatgpt-now-shes-one-of-the-worlds-top-investors/ (搜索摘要) ; https://en.wikipedia.org/wiki/Sarah_Guo (搜索摘要)</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>v-wing-vc</t>
+          <t>v-conviction</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>SimReal: RL environments for finance, built by ex-Jane Street and Citadel quants (seed)</t>
+          <t>Ex-Jane Street quants building RL environments, supplying Surge AI</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>Hi Chris,
-I'm [Your name], co-founder of SimReal (simreal.co). We build RL environments and verifiers where models do real work and are scored on real outcomes.
-Your RL environments piece argued verification, not model capability, is what makes automation durable; verifiers are the core of what we build for finance.
-Our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke), raising a $20M seed and in conversations with tier-1 funds.
-Worth 20 minutes? Happy to send the deck.
+          <t>Hi Sarah,
+Conviction led Trajectory's seed for continual learning in May; we build the finance environments where that kind of learning gets scored against real outcomes.
+I'm [Your name], co-founder of SimReal. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke).
+SimReal builds RL environments and verifiers where AI models do real work and are scored on real outcomes.
+Traction: our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up.
+We're raising a $20M seed and are in conversations with tier-1 funds. Deck: [Deck link]. Worth 20 minutes next week?
 Best,
 [Your name]
 Co-founder, SimReal
@@ -1544,12 +1554,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>A 组：最匹配，最后发</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Eniac Ventures</t>
+          <t>General Catalyst</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1564,17 +1574,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Hadley Harris</t>
+          <t>Yuri Sagalov</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>联合创始人、General Partner（AI 原生、数据基础设施方向）</t>
+          <t>Managing Director（负责 GC 美国种子投资）</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>pitch@eniac.vc</t>
+          <t>seed@generalcatalyst.com</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1584,51 +1594,52 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>第一句写明请转交 Hadley Harris（Could you pass this to Hadley Harris?）</t>
+          <t>第一句写明请转交 Yuri Sagalov（Could you pass this to Yuri Sagalov?）</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Eniac joined Origin Lab's seed to turn game worlds into AI training data; we turn financial markets into RL environments for the same labs.</t>
+          <t>You led Arga's seed and argued that repeatable sandboxes matter even more for agents; we've built that for finance, where outcomes settle in real markets.</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>种子轮投资。</t>
+          <t>A 组（最后发）：最匹配、最想拿下，话术成熟后再发。 原排序理由：合伙人专做种子，刚领投企业 RL 沙箱，观点和我们高度一致；要回应与 Mercor 的关系。</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>负责 Origin Lab 的合伙人未确认。</t>
+          <t>GC 深度绑定 Mercor，且已投 Arga（企业软件沙箱），需讲清金融垂直差异。</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>pitch@eniac.vc（Eniac 官方 Medium 投递说明 https://eniacvc.medium.com/eniac-ventures-is-ready-for-your-pitches-again-27fa23f5e5d8）</t>
+          <t>seed@generalcatalyst.com（官方投递，GC 种子项目；精确搜索该地址，首条结果是官网 https://www.generalcatalyst.com/stories/seed-at-general-catalyst ，搜索摘要） ；https://www.generalcatalyst.com/stories/seed-at-general-catalyst（种子项目页）</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>https://www.eniac.vc/team (搜索摘要) ; https://signal.nfx.com/investors/hadley-harris (搜索摘要)</t>
+          <t>https://www.generalcatalyst.com/team/yuri-sagalov (搜索摘要) ; https://x.com/yuris/status/1911815110412353667 (搜索摘要)</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>v-eniac-ventures</t>
+          <t>v-general-catalyst</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>SimReal: RL environments for finance, built by ex-Jane Street and Citadel quants (seed)</t>
+          <t>Ex-Jane Street quants building RL environments, supplying Surge AI</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>Hi Hadley,
-I'm [Your name], co-founder of SimReal (simreal.co). We build RL environments and verifiers where models do real work and are scored on real outcomes.
-Eniac joined Origin Lab's seed to turn game worlds into AI training data; we turn financial markets into RL environments for the same labs.
-Our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke), raising a $20M seed and in conversations with tier-1 funds.
-Worth 20 minutes? Happy to send the deck.
+          <t>Hi Yuri,
+You led Arga's seed and argued that repeatable sandboxes matter even more for agents; we've built that for finance, where outcomes settle in real markets.
+I'm [Your name], co-founder of SimReal. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke).
+SimReal builds RL environments and verifiers where AI models do real work and are scored on real outcomes.
+Traction: our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up.
+We're raising a $20M seed and are in conversations with tier-1 funds. Deck: [Deck link]. Worth 20 minutes next week?
 Best,
 [Your name]
 Co-founder, SimReal
@@ -1642,12 +1653,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>A 组：最匹配，最后发</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Lux Capital</t>
+          <t>Laude Ventures</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1662,17 +1673,17 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Grace Isford</t>
+          <t>Andy Konwinski</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>联合创始人（Laude Ventures / Laude Institute，Databricks、Perplexity 联合创始人）</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>info@luxcapital.com</t>
+          <t>hello@laude.vc</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1682,51 +1693,52 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>第一句写明请转交 Grace Isford（Could you pass this to Grace Isford?）</t>
+          <t>第一句写明请转交 Andy Konwinski（Could you pass this to Andy Konwinski?）</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Lux backed Applied Compute twice as enterprises start training their own models; we supply the RL environments and expert data those runs need, starting with finance and accounting.</t>
+          <t>Laude described backing Arena as turning research-driven evaluation into AI infrastructure; we're doing that for finance, where models are scored by real market outcomes.</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>持续加注后训练平台，没有竞品冲突。</t>
+          <t>A 组（最后发）：最匹配、最想拿下，话术成熟后再发。</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Applied Compute 可能自建环境；Grace 与 Applied Compute 的关系仅见 Lux 公司页列名。</t>
+          <t>偏好研究出身的技术团队。</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>info@luxcapital.com（官网联系页 https://www.luxcapital.com/contact）</t>
+          <t>hello@laude.vc（官方通用；精确搜索该地址，结果指向 laude.vc 官网页面，搜索摘要） ；https://laude.vc（官网联系表单）</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>https://www.luxcapital.com/people/grace-isford (搜索摘要) ; https://www.luxcapital.com/companies/applied-compute (搜索摘要)</t>
+          <t>https://laude.vc/team/andy-konwinski (搜索摘要) ; https://laude.vc/team (搜索摘要)</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>v-lux-capital</t>
+          <t>v-laude-ventures</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>SimReal: RL environments for finance, built by ex-Jane Street and Citadel quants (seed)</t>
+          <t>Ex-Jane Street quants building RL environments, supplying Surge AI</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>Hi Grace,
-I'm [Your name], co-founder of SimReal (simreal.co). We build RL environments and verifiers where models do real work and are scored on real outcomes.
-Lux backed Applied Compute twice as enterprises start training their own models; we supply the RL environments and expert data those runs need, starting with finance and accounting.
-Our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke), raising a $20M seed and in conversations with tier-1 funds.
-Worth 20 minutes? Happy to send the deck.
+          <t>Hi Andy,
+Laude described backing Arena as turning research-driven evaluation into AI infrastructure; we're doing that for finance, where models are scored by real market outcomes.
+I'm [Your name], co-founder of SimReal. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke).
+SimReal builds RL environments and verifiers where AI models do real work and are scored on real outcomes.
+Traction: our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up.
+We're raising a $20M seed and are in conversations with tier-1 funds. Deck: [Deck link]. Worth 20 minutes next week?
 Best,
 [Your name]
 Co-founder, SimReal
@@ -1740,12 +1752,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>A 组：最匹配，最后发</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Tower Research Ventures</t>
+          <t>Menlo Ventures</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1755,76 +1767,77 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>海外（美国，纽约）</t>
+          <t>海外（美国）</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Jared Young</t>
+          <t>Deedy Das</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Director of Venture Capital</t>
+          <t>Partner（种子到 B 轮 AI/基础设施）</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>ventures@tower-research.com</t>
+          <t>deedy@menlovc.com</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>官方投递</t>
+          <t>个人公开</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>第一句写明请转交 Jared Young（Could you pass this to Jared Young?）</t>
+          <t>直接写给 Deedy Das</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>TRV has been hosting AI x Wall Street and AI-agent events for the trading world; we're ex-quants building RL environments that train agents on real market data.</t>
+          <t>Your July map counted 50+ companies selling data and RL environments to labs, with most revenue in four players; we're a finance-specialist entrant with quant founders and our own experts.</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Pre-seed/种子投资；Tower 交易团队也可能是 Xitadel 用户。</t>
+          <t>A 组（最后发）：最匹配、最想拿下，话术成熟后再发。 原排序理由：对赛道最熟的合伙人之一；但持有 Fleet、Mercor，要讲清差异。</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>规模小；投资组合偏应用 AI 与加密。</t>
+          <t>已投 Fleet、Mercor 两家直接竞品。</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>ventures@tower-research.com（官网 Ventures 页，搜索摘要 https://tower-research.com/ventures/）</t>
+          <t>https://debarghyadas.com/ (搜索摘要：精确搜索该地址，首条结果是本人主页)</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>https://tower-research.com/ventures/ (搜索摘要)</t>
+          <t>https://menlovc.com/team/deedy-das/ (搜索摘要) ; https://slush.org/2026-speakers/deedy-das (搜索摘要)</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>v-tower-research-ventures</t>
+          <t>v-menlo-ventures</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>SimReal: RL environments for finance, built by ex-Jane Street and Citadel quants (seed)</t>
+          <t>Ex-Jane Street quants building RL environments, supplying Surge AI</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>Hi Jared,
-I'm [Your name], co-founder of SimReal (simreal.co). We build RL environments and verifiers where models do real work and are scored on real outcomes.
-TRV has been hosting AI x Wall Street and AI-agent events for the trading world; we're ex-quants building RL environments that train agents on real market data.
-Our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke), raising a $20M seed and in conversations with tier-1 funds.
-Worth 20 minutes? Happy to send the deck.
+          <t>Hi Deedy,
+Your July map counted 50+ companies selling data and RL environments to labs, with most revenue in four players; we're a finance-specialist entrant with quant founders and our own experts.
+I'm [Your name], co-founder of SimReal. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke).
+SimReal builds RL environments and verifiers where AI models do real work and are scored on real outcomes.
+Traction: our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up.
+We're raising a $20M seed and are in conversations with tier-1 funds. Deck: [Deck link]. Worth 20 minutes next week?
 Best,
 [Your name]
 Co-founder, SimReal
@@ -1838,12 +1851,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>第 3 批：最重要，话术熟了再发</t>
+          <t>A 组：最匹配，最后发</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>General Catalyst</t>
+          <t>Wing VC</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1858,71 +1871,72 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Yuri Sagalov</t>
+          <t>Chris Zeoli</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Managing Director（负责 GC 美国种子投资）</t>
+          <t>Partner（数据基础设施/AI 基础设施）</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>seed@generalcatalyst.com</t>
+          <t>chris@wing.vc</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>官方投递</t>
+          <t>个人公开</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>第一句写明请转交 Yuri Sagalov（Could you pass this to Yuri Sagalov?）</t>
+          <t>直接写给 Chris Zeoli</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>You led Arga's seed and argued that repeatable sandboxes matter even more for agents; we've built that for finance, where outcomes settle in real markets.</t>
+          <t>Your RL environments piece argued verification, not model capability, is what makes automation durable; verifiers are the core of what we build for finance.</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>合伙人专做种子，刚领投企业 RL 沙箱，观点和我们高度一致；要回应与 Mercor 的关系。</t>
+          <t>A 组（最后发）：最匹配、最想拿下，话术成熟后再发。 原排序理由：写过 RL 环境市场研究，强调验证，正对我们的卖点；但持有 Bespoke，偏 A 轮。</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>GC 深度绑定 Mercor，且已投 Arga（企业软件沙箱），需讲清金融垂直差异。</t>
+          <t>已投 Bespoke Labs（RL 环境），偏 A 轮。</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>seed@generalcatalyst.com（官方投递，GC 种子项目；精确搜索该地址，首条结果是官网 https://www.generalcatalyst.com/stories/seed-at-general-catalyst ，搜索摘要） ；https://www.generalcatalyst.com/stories/seed-at-general-catalyst（种子项目页）</t>
+          <t>https://x.com/chriszeoli ; https://www.wing.vc/team (搜索摘要：本人公开写法为 "Chris [at] wing.vc"，精确搜索结果指向本人 X 和 Wing 团队页)</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>https://www.generalcatalyst.com/team/yuri-sagalov (搜索摘要) ; https://x.com/yuris/status/1911815110412353667 (搜索摘要)</t>
+          <t>https://www.wing.vc/people/chris-zeoli (搜索摘要)</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>v-general-catalyst</t>
+          <t>v-wing-vc</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>SimReal: RL environments for finance, built by ex-Jane Street and Citadel quants (seed)</t>
+          <t>Ex-Jane Street quants building RL environments, supplying Surge AI</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>Hi Yuri,
-I'm [Your name], co-founder of SimReal (simreal.co). We build RL environments and verifiers where models do real work and are scored on real outcomes.
-You led Arga's seed and argued that repeatable sandboxes matter even more for agents; we've built that for finance, where outcomes settle in real markets.
-Our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke), raising a $20M seed and in conversations with tier-1 funds.
-Worth 20 minutes? Happy to send the deck.
+          <t>Hi Chris,
+Your RL environments piece argued verification, not model capability, is what makes automation durable; verifiers are the core of what we build for finance.
+I'm [Your name], co-founder of SimReal. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke).
+SimReal builds RL environments and verifiers where AI models do real work and are scored on real outcomes.
+Traction: our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up.
+We're raising a $20M seed and are in conversations with tier-1 funds. Deck: [Deck link]. Worth 20 minutes next week?
 Best,
 [Your name]
 Co-founder, SimReal
@@ -1936,7 +1950,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>第 3 批：最重要，话术熟了再发</t>
+          <t>A 组：最匹配，最后发</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1982,7 +1996,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>量化机构本身，背景最契合，今年连投两家评测公司；最重要，放最后，等话术成熟再发。</t>
+          <t>A 组（最后发）：最匹配、最想拿下，话术成熟后再发。 原排序理由：量化机构本身，背景最契合，今年连投两家评测公司；最重要，放最后，等话术成熟再发。</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2007,16 +2021,17 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>SimReal: RL environments for finance, built by ex-Jane Street and Citadel quants (seed)</t>
+          <t>Ex-Jane Street quants building RL environments, supplying Surge AI</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
           <t>Hi HRT Ventures team,
-I'm [Your name], co-founder of SimReal (simreal.co). We build RL environments and verifiers where models do real work and are scored on real outcomes.
 HRT Ventures joined Vals AI's Series A in August; we build trading RL environments, and our founders come from the same quant world.
-Our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke), raising a $20M seed and in conversations with tier-1 funds.
-Worth 20 minutes? Happy to send the deck.
+I'm [Your name], co-founder of SimReal. We're four quants from Jane Street, Citadel, Millennium and Optiver (Cambridge, LSE, Duke).
+SimReal builds RL environments and verifiers where AI models do real work and are scored on real outcomes.
+Traction: our trading environment, Xitadel, lifted Qwen3.8-27B's trading performance 12% on unseen market data, reproduced across independent runs. We already supply Surge AI and AfterQuery, and 7,000+ domain experts have signed up.
+We're raising a $20M seed and are in conversations with tier-1 funds. Deck: [Deck link]. Worth 20 minutes next week?
 Best,
 [Your name]
 Co-founder, SimReal
@@ -2062,7 +2077,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>批次</t>
+          <t>分组</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -2127,17 +2142,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>第 1 批：先发</t>
+          <t>C 组：先发练手</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Acrew Capital</t>
+          <t>Adam D'Angelo（Quora CEO）</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>VC</t>
+          <t>天使</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2147,12 +2162,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Asad Khaliq</t>
+          <t>Adam D'Angelo</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Founding Partner</t>
+          <t>Founder &amp; CEO, Quora</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -2162,27 +2177,27 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>You co-led Veris AI's seed, backing agent training through experience rather than evaluation; we build that experience for finance agents, with verifiers checked against real market data.</t>
+          <t>You backed Mechanize's seed, and Google has since brought its RL environment team into DeepMind; we're building that category for finance and accounting.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>同时投了模拟环境和专家数据两类公司，最容易听懂我们的定位；种子阶段对口。</t>
+          <t>C 组（先发练手）：匹配度相对低，用这一组的回复打磨话术。</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>已投 Veris AI（相邻竞品）与 Invisible Technologies（专家数据竞品）。</t>
+          <t>可及性低；兼任 OpenAI 董事会成员（未在本轮单独核实）。</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>https://www.acrewcapital.com/team-members/asad-khaliq (搜索摘要) ; https://www.crunchbase.com/person/asad-khaliq (搜索摘要)</t>
+          <t>https://en.wikipedia.org/wiki/Adam_D%27Angelo (搜索摘要) ; https://www.crunchbase.com/person/adam-dangelo (搜索摘要)</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>v-acrew-capital</t>
+          <t>v-adam-dangelo</t>
         </is>
       </c>
     </row>
@@ -2192,17 +2207,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>第 1 批：先发</t>
+          <t>C 组：先发练手</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Decibel</t>
+          <t>Alex Atallah（OpenRouter CEO）</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>VC</t>
+          <t>天使</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -2212,42 +2227,42 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Alessio Fanelli</t>
+          <t>Alex Atallah</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Partner &amp; CTO</t>
+          <t>Co-founder &amp; CEO, OpenRouter</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>官网 Connect 页 https://www.decibel.vc/connect</t>
+          <t>个人主页 https://alexatallah.com/（无公开邮箱）</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>You co-led Veris AI's seed as the environment layer enterprise AI was missing; we build that layer for finance, where agent outcomes settle against real markets.</t>
+          <t>You backed Mechanize when RL environments were still a niche bet; we're building them for finance, with verifiers checked against real market data.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>种子基金，领投过 agent 模拟环境；阶段完全对口。</t>
+          <t>C 组（先发练手）：匹配度相对低，用这一组的回复打磨话术。</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>已投 Veris AI（企业 RL 环境，相邻竞品）。</t>
+          <t>据报道 Stripe 2026-08 同意收购 OpenRouter，交割期精力有限。</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>https://www.decibel.vc/team/alessio-fanelli (搜索摘要) ; https://www.decibel.vc/articles/welcoming-alessio-fanelli-as-decibels-newest-partner (搜索摘要)</t>
+          <t>https://ai.engineer/speakers/alex-atallah (搜索摘要) ; https://www.crunchbase.com/person/alex-atallah-912d (搜索摘要)</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>v-decibel</t>
+          <t>v-alex-atallah</t>
         </is>
       </c>
     </row>
@@ -2257,62 +2272,62 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>第 1 批：先发</t>
+          <t>C 组：先发练手</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Dylan Patel（SemiAnalysis）</t>
+          <t>Antler Singapore</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>天使</t>
+          <t>加速器</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>海外（美国）</t>
+          <t>海外（新加坡）</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Dylan Patel</t>
+          <t>Jussi Salovaara</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Founder, CEO &amp; Chief Analyst, SemiAnalysis</t>
+          <t>Co-founder, Antler; Managing Partner, Asia (Singapore-based)</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>未找到</t>
+          <t>Antler Singapore 官网申请 https://www.antler.co/location/singapore (搜索摘要；下一期驻留 2026-10-05 开始)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>You angel-invested in HUD and co-wrote SemiAnalysis's piece on RL environments and data foundries; we're one of those foundries, focused on finance environments and verifiers.</t>
+          <t>You've said you'd rather back founders with deep domain expertise than new AI coding startups; we're four quants turning trading and accounting expertise into RL environments and verifiers for LLMs.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>活跃的 RL 基础设施天使，愿意投早期团队。</t>
+          <t>C 组（先发练手）：匹配度相对低，用这一组的回复打磨话术。</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>无直接冲突；已投 HUD、Prime Intellect。</t>
+          <t>Antler 以 day-zero 驻留模式为主，已成型团队可能只适合其后续轮；新加坡团队层面对接人未找到。</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>https://semianalysis.com/dylan-patel/ (搜索摘要) ; https://www.hud.ai/blog/announcing-16m-series-a (搜索摘要)</t>
+          <t>https://www.crunchbase.com/person/jussi-salovaara (搜索摘要) ; https://technode.global/2026/06/22/antler-showcases-28-startups-across-asia-building-autonomous-ai-systems-beyond-copilots/ (搜索摘要) ; https://sg.linkedin.com/in/jsalovaara (搜索摘要)</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>v-dylan-patel</t>
+          <t>v-antler-singapore</t>
         </is>
       </c>
     </row>
@@ -2322,17 +2337,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>第 1 批：先发</t>
+          <t>C 组：先发练手</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>Dheeraj Pandey（DevRev CEO）</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>VC</t>
+          <t>天使</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -2342,12 +2357,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Alexis Ohanian</t>
+          <t>Dheeraj Pandey</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Founder</t>
+          <t>Co-founder, CEO &amp; Chairman, DevRev</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -2357,27 +2372,27 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>You led Deeptune's seed and then watched Mercor buy it for its RL environments; we're building that category for finance, with verifiers checked against real market data.</t>
+          <t>You angel-invested in Bespoke Labs' seed as RL environments for long-horizon agents took off; we build those environments for finance, from month-end close to trading.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>投过 RL 环境公司，且那家已被收购，组合里出现空位。</t>
+          <t>C 组（先发练手）：匹配度相对低，用这一组的回复打磨话术。</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>联系方式仅见第三方数据库，未写入。</t>
+          <t>无冲突。</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>https://x.com/alexisohanian/status/2034760840562581881 (搜索摘要) ; https://en.wikipedia.org/wiki/Alexis_Ohanian (搜索摘要)</t>
+          <t>https://devrev.ai/authors/dheeraj (搜索摘要) ; https://en.wikipedia.org/wiki/Dheeraj_Pandey (搜索摘要)</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>v-seven-seven-six</t>
+          <t>v-dheeraj-pandey</t>
         </is>
       </c>
     </row>
@@ -2387,12 +2402,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>第 1 批：先发</t>
+          <t>C 组：先发练手</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Abstract Ventures</t>
+          <t>Gobi Partners GBA (Alibaba Entrepreneurs Fund GP)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2402,47 +2417,47 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>海外（美国）</t>
+          <t>海外（香港）</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Ramtin Naimi</t>
+          <t>Chibo Tang</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>创始人、General Partner</t>
+          <t>Managing Partner, Gobi Partners (Gobi GBA; GP of Alibaba Hong Kong Entrepreneurs Fund)</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>未找到</t>
+          <t>阿里巴巴香港创业者基金投资页 https://www.ent-fund.org/en/investment/hk (搜索摘要) ; https://www.gobi.vc/ (搜索摘要)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Abstract joined Deeptune's Series A for agent training gyms, accountant workflows included, before Mercor bought it; we build finance and month-end close environments in that category.</t>
+          <t>You launched the Gobi–HKU Fund I in March to back AI spin-offs; we're Cambridge, LSE and Duke quants building finance RL environments and verifiers for LLM post-training, raising our seed.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>RL 环境和后训练两边都跟投过；Deeptune 已并入 Mercor，竞品冲突减弱。</t>
+          <t>C 组（先发练手）：匹配度相对低，用这一组的回复打磨话术。</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>无直接冲突。</t>
+          <t>AEF 要求香港创始人或在港运营；Gobi–HKU 基金只投港大衍生项目；HKIC 为该基金出资方（HKIC 已在 V2 种子名单）。</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>https://www.crunchbase.com/person/ramtin-naimi (搜索摘要) ; https://signal.nfx.com/investors/ramtin-naimi (搜索摘要)</t>
+          <t>https://www.hku.hk/press/press-releases/detail/29006.html (搜索摘要) ; https://technode.global/2026/03/26/university-of-hong-kong-asia-focused-gobi-partners-launch-joint-fund-to-support-startups-innovations/ (搜索摘要)</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>v-abstract-ventures</t>
+          <t>v-gobi-partners-gba</t>
         </is>
       </c>
     </row>
@@ -2452,62 +2467,62 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>第 1 批：先发</t>
+          <t>C 组：先发练手</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Elad Gil</t>
+          <t>Golden Gate Ventures</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>天使</t>
+          <t>VC</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>海外（美国）</t>
+          <t>海外（新加坡）</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Elad Gil</t>
+          <t>Vinnie Lauria</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>个人投资人（2025 年起管理机构化基金）</t>
+          <t>Founding Partner</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>未找到</t>
+          <t>官网 https://www.goldengate.vc/ (搜索摘要；投递入口未在摘要中看到)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>You're reported to be in talks to lead Applied Compute's new round; as more companies train their own models with RL, they need domain environments, and we build them for finance.</t>
+          <t>You led The Librarian's seed and called it one of the few AI launches that changes how people work; we build the finance RL environments and verifiers that make assistants reliable for professionals.</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>信号型天使，后训练、评测、数据策展都投过；投过 HeyGen。</t>
+          <t>C 组（先发练手）：匹配度相对低，用这一组的回复打磨话术。</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Applied Compute 轮次尚未确定；种子单笔可能较小，可及性低。</t>
+          <t>偏东南亚/中东应用层，AI 训练数据基础设施非其主赛道。</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>https://aiweekly.co/alerts/applied-compute-in-talks-for-3b-round-led-by-elad-gil (搜索摘要) ; https://www.thevccorner.com/p/elad-gil-solo-super-angel-solo-gp (搜索摘要)</t>
+          <t>https://www.goldengate.vc/team/vinnie-lauria (搜索摘要) ; https://technode.global/2025/11/14/the-librarian-raises-2m-in-seed-round-led-by-golden-gate-ventures/ (搜索摘要)</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>v-elad-gil</t>
+          <t>v-golden-gate-ventures</t>
         </is>
       </c>
     </row>
@@ -2517,12 +2532,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>第 1 批：先发</t>
+          <t>C 组：先发练手</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Episode 1 Ventures</t>
+          <t>Granite Asia</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2532,47 +2547,47 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>海外（英国，伦敦）</t>
+          <t>海外（新加坡）</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Simon Murdoch</t>
+          <t>Jenny Lee</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Managing Partner</t>
+          <t>Senior Managing Partner (Singapore; seed–Series A in AI, fintech, enterprise)</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>官网 submit your deck 入口 https://www.episode1.com/</t>
+          <t>官网 https://www.graniteasia.com/ (搜索摘要；投递入口未在摘要中看到)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>You led Poindexter Labs' seed as it signed a frontier lab directly; we sell the same labs expert data and RL environments, built by Cambridge and LSE quants.</t>
+          <t>You lead Granite Asia's seed-to-Series A investing across AI and fintech; we sit at that intersection, building finance RL environments, verifiers and expert data for LLM post-training.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>欧洲少数领投 AI 训练数据种子轮的基金，竞争少、回复率可能更高。</t>
+          <t>C 组（先发练手）：匹配度相对低，用这一组的回复打磨话术。</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>已投 Poindexter（专家数据竞品）；Poindexter 由哪位合伙人负责未知。</t>
+          <t>Jenny Lee 为明星合伙人、冷邮件回复率低；2026 年重心含 AI IPO 基金与成长期；钩子较弱（岗位事实而非具体交易）。</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>https://www.episode1.com/team (搜索摘要) ; https://www.crunchbase.com/person/simon-murdoch (搜索摘要)</t>
+          <t>https://www.graniteasia.com/who-we-are?p=jenny-lee (搜索摘要) ; https://signal.nfx.com/investors/jenny-lee (搜索摘要) ; https://technode.global/2026/02/23/dbs-and-granite-asia-partner-to-launch-110m-ai-ipo-fund-for-asias-next-generation-companies/ (搜索摘要)</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>v-episode-1</t>
+          <t>v-granite-asia</t>
         </is>
       </c>
     </row>
@@ -2582,12 +2597,12 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>第 1 批：先发</t>
+          <t>C 组：先发练手</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Gradient Ventures</t>
+          <t>Greenfield Partners</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2597,17 +2612,17 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>海外（美国）</t>
+          <t>海外（以色列/美国）</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Darian Shirazi</t>
+          <t>Itay Inbar</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>General Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2617,27 +2632,27 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Gradient joined Arga's seed for enterprise agent sandboxes and just closed a $220M seed fund; we're raising our seed to build RL environments for finance.</t>
+          <t>You led Patronus's Series B arguing simulations are becoming essential for AI to learn; we build simulation environments where outcomes settle in real markets, starting with trading.</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Google 旗下种子基金，投过企业 RL 沙箱；Google 本身是 RL 环境大买家。</t>
+          <t>C 组（先发练手）：匹配度相对低，用这一组的回复打磨话术。</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Gradient 已从 Google 独立（Google 仍为 LP）；Arga 由哪位合伙人负责未知。</t>
+          <t>B 轮阶段；Patronus 为评测/仿真邻近公司；有媒体（The Dissent）质疑该轮缺少 SEC 备案。</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>https://www.businesswire.com/news/home/20260317890946/en/Gradient-Raises-$220M-Fifth-Fund-To-Seed-Next-Generation-of-AI-Founders (搜索摘要)</t>
+          <t>https://www.prnewswire.com/news-releases/patronus-ai-raises-50-million-series-b-and-unveils-first-digital-world-models-for-ai-agent-training-and-simulation-302811248.html (搜索摘要) ; https://www.linkedin.com/in/itay-inbar-gp/ (搜索摘要)</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>v-gradient-ventures</t>
+          <t>v-greenfield-partners</t>
         </is>
       </c>
     </row>
@@ -2647,17 +2662,17 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>第 1 批：先发</t>
+          <t>C 组：先发练手</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Scribble Ventures</t>
+          <t>Ian Livingstone（Keycard CEO）</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>VC</t>
+          <t>天使</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -2667,42 +2682,42 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Stu Smith</t>
+          <t>Ian Livingstone</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Partner（发布 Proximal 领投帖）</t>
+          <t>Co-founder &amp; CEO, Keycard</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>https://www.scribble.vc（官网 Contact 入口）</t>
+          <t>未找到</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Scribble led Proximal's round for long-horizon coding RL environments with fuzzy verifiers; we build the same kind of verified environments for trading and accounting.</t>
+          <t>You angel-invested in Veris AI's seed to train agents through simulated experience; we build that experience for finance agents, with verifiers checked against real market data.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>领投过 RL 环境公司的种子轮，单笔小（约 30 万–75 万美元）、决策快；Proximal 做编码，和金融不重叠。</t>
+          <t>C 组（先发练手）：匹配度相对低，用这一组的回复打磨话术。</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>已投 Proximal（代码 RL 环境），方向不同但同赛道。</t>
+          <t>同名人物较多（另有游戏业 Ian Livingstone），发信前确认。</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>https://www.scribble.vc/stu (搜索摘要) ; https://www.linkedin.com/posts/imstusmith_excited-to-finally-share-that-scribble-ventures-activity-7430007099004432384-cqbR (搜索摘要)</t>
+          <t>https://www.crunchbase.com/person/ian-livingstone-95d7 (搜索摘要) ; https://fintech.global/2025/10/23/keycard-secures-38m-to-advance-ai-agent-security/ (搜索摘要)</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>v-scribble-ventures</t>
+          <t>v-ian-livingstone</t>
         </is>
       </c>
     </row>
@@ -2712,62 +2727,62 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>第 1 批：先发</t>
+          <t>C 组：先发练手</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>SV Angel</t>
+          <t>Iterative</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>VC</t>
+          <t>加速器</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>海外（美国）</t>
+          <t>海外（新加坡）</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Topher Conway</t>
+          <t>Hsu Ken Ooi</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Managing Partner</t>
+          <t>Co-Founder &amp; Managing Partner</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>未找到</t>
+          <t>官网申请 https://www.iterative.vc/ (搜索摘要)；Office Hours 页 https://www.iterative.vc/post/office-hours-with-iterative-partners (搜索摘要)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>SV Angel is in the seed rounds of Arga and Origin Lab this year; we'd like to add a finance-focused RL environment company to that set.</t>
+          <t>Iterative co-led i10X's pre-seed in January 2026; we're quant founders building executable finance RL environments and verifiers for LLM post-training, and we're raising our seed.</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>本赛道跟投最活跃的种子基金之一；投过 HeyGen，对华人团队友好。</t>
+          <t>C 组（先发练手）：匹配度相对低，用这一组的回复打磨话术。</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>已投 Fleet；原种子基金负责人 Beth Turner 已离开创立 Valkyrie。</t>
+          <t>Iterative 只投东南亚相关公司，SimReal 需有新加坡实体或东南亚关联；票面较小。</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>https://svangel.com/about/team (搜索摘要) ; https://www.crunchbase.com/person/topher-conway (搜索摘要)</t>
+          <t>https://www.iterative.vc/team (搜索摘要) ; https://hsukenooi.com/ (搜索摘要) ; https://www.crunchbase.com/person/hsu-ken-ooi (搜索摘要)</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>v-sv-angel</t>
+          <t>v-iterative</t>
         </is>
       </c>
     </row>
@@ -2777,62 +2792,62 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>第 1 批：先发</t>
+          <t>C 组：先发练手</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Yash Patil（Applied Compute CEO）</t>
+          <t>Peak XV Partners (Surge)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>天使</t>
+          <t>加速器</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>海外（美国）</t>
+          <t>海外（新加坡）</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Yash Patil</t>
+          <t>Rajan Anandan</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Co-founder &amp; CEO, Applied Compute</t>
+          <t>Managing Director, Peak XV Partners; leads Surge (seed program)</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>未找到</t>
+          <t>Surge 滚动申请页 https://surge.peakxv.com/ (搜索摘要；2026-09 新一期开营，官网 FAQ 称申请滚动开放 https://surge.peakxv.com/faqs)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>You angel-invested in Deeptune while Applied Compute trains custom models for enterprises; we build finance and accounting RL environments that could feed those runs.</t>
+          <t>Surge 11 backed finance-AI teams like OnFinance and Finster; we build what sits upstream of such products: executable finance RL environments, verifiers and expert data, from a quant founding team.</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>天使投过 RL 环境；Applied Compute 同时是潜在客户，一次沟通两种机会。</t>
+          <t>C 组（先发练手）：匹配度相对低，用这一组的回复打磨话术。</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Applied Compute 可能自建环境。</t>
+          <t>Rajan 常驻德里、主看印度；Surge 以印度/东南亚为主，SimReal 若非新加坡/印度实体需说明区域相关性；2026-02 有合伙人离职。</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>https://www.crunchbase.com/person/yash-patil-f81e (搜索摘要) ; https://www.forbes.com/sites/richardnieva/2026/09/01/applied-compute-openai-the-ex-openai-guys-building-cheaper-open-source-alternative/ (搜索摘要)</t>
+          <t>https://www.peakxv.com/team/rajan-anandan (搜索摘要) ; https://www.forbesindia.com/audio/forbes-india-tech-conver-sations/peak-xvs-shailendra-singh-rajan-anandan-open-up-on-their-dreams-for-surge/94447 (搜索摘要)</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>v-yash-patil</t>
+          <t>v-peak-xv-surge</t>
         </is>
       </c>
     </row>
@@ -2842,12 +2857,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>第 1 批：先发</t>
+          <t>C 组：先发练手</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>BoxGroup</t>
+          <t>Sky9 Capital</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2862,42 +2877,42 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>David Tisch</t>
+          <t>Ron Cao</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Managing Partner</t>
+          <t>Founding Partner</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>未找到</t>
+          <t>https://www.sky9capital.com/contact/（搜索摘要）</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>BoxGroup joined Arga's seed for enterprise agent sandboxes in August; we build the finance counterpart, with trading and month-end close environments.</t>
+          <t>You led ProducerAI's seed in 2023 before Google acquired it; we're quant founders building executable finance RL environments, verifiers and expert data, and we're raising our seed.</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>早早投了两家金融背景团队做的 AI 数据/环境公司，看得懂我们的背景。</t>
+          <t>C 组（先发练手）：匹配度相对低，用这一组的回复打磨话术。</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>同时是 AfterQuery 早期股东；负责 Arga 的合伙人不明。</t>
+          <t>对 RL 环境/数据赛道的认知未经证实；invest@sky9capital.com 据第三方说明只用于 LP 询问，未采用。</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/BoxGroup (搜索摘要) ; https://theorg.com/org/boxgroup (搜索摘要)</t>
+          <t>https://www.sky9capital.com/news/sky9-capital-portfolio-company-producerai-acquired-by-google/（搜索摘要） ; https://www.bloomberg.com/profile/person/16685992（搜索摘要） ; https://www.linkedin.com/in/sky9roncao/（搜索摘要）</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>v-boxgroup</t>
+          <t>v-sky9-capital</t>
         </is>
       </c>
     </row>
@@ -2907,12 +2922,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>第 1 批：先发</t>
+          <t>C 组：先发练手</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Emergence Capital</t>
+          <t>Vanara Capital</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2927,34 +2942,42 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
+          <t>Hayden Lekacz</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>联合创始人（Invisible 董事）</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>未找到</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>未找到</t>
-        </is>
-      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Emergence joined Arga's seed to give enterprise agents resettable practice environments; we build the same kind of environments for finance, from month-end close to trading.</t>
+          <t>Vanara led Invisible's $100M round as a foundational layer of AI infrastructure; we're building that layer for finance, with quant founders and expert data.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>投过企业软件 RL 沙箱，种子到 A 轮；据摘要是 Genspark 早期投资人（低置信度）。</t>
+          <t>C 组（先发练手）：匹配度相对低，用这一组的回复打磨话术。</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Arga 负责人未公开；每位合伙人每年只投一家，门槛高。</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
+          <t>成长期基金，2026 年未见新动作；Invisible 为专家数据竞品。</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.businesswire.com/news/home/20250916425748/en/Invisible-Technologies-Raises-$100-Million-to-Power-the-Next-Generation-of-AI-Infrastructure-for-the-Enterprise (搜索摘要) ; https://www.eenewseurope.com/en/invisible-technologies-secures-100m-in-growth-funding-led-by-tpg-spinoff/ (搜索摘要)</t>
+        </is>
+      </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>v-emergence-capital</t>
+          <t>v-vanara-capital</t>
         </is>
       </c>
     </row>
@@ -2964,12 +2987,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>第 1 批：先发</t>
+          <t>C 组：先发练手</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Pear VC</t>
+          <t>Vertex Ventures Southeast Asia &amp; India</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2979,39 +3002,47 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>海外（美国）</t>
+          <t>海外（新加坡）</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>未找到</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr"/>
+          <t>Jessica Koh</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Senior Executive Director, Investment</t>
+        </is>
+      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>PearX 申请 https://pear.vc/pearx-application/ ；Pitch 页 https://www.pear.vc/pitch</t>
+          <t>https://www.vertexventures.sg/apply/（搜索摘要）</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Pear backed Vals AI from seed through its a16z-led Series A as professional-task evals took off; we build RL environments and verifiers for finance tasks, one step past evaluation.</t>
+          <t>You led FORMAS.AI's pre-seed, noting AI is moving to integrated platforms with fine-tuning; we build finance RL environments and verifiers that feed that post-training loop.</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>pre-seed/种子基金，评测公司股东，没有 RL 环境竞品。</t>
+          <t>C 组（先发练手）：匹配度相对低，用这一组的回复打磨话术。</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>负责 Vals 的合伙人未找到；Vals 在金融评测上与我们有重叠。</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr"/>
+          <t>聚焦东南亚和印度，需要新加坡主体；淡马锡本身以后期为主，未找到早期对接人（本行以 Vertex SEA&amp;I 代替）。</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vertexventures.sg/news/formas-ai-raises-us-3-98-million-in-oversubscribed-pre-seed-round-to-build-the-ai-native-design-workspace-for-architecture/（搜索摘要） ; https://technode.global/2026/04/29/singapores-formas-ai-raises-3-98m-in-pre-seed-round-led-by-vertex-ventures-southeast-asia-india/（搜索摘要）</t>
+        </is>
+      </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>v-pear-vc</t>
+          <t>v-vertex-ventures-sea</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3052,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>C 组：先发练手</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Altos Ventures</t>
+          <t>Wavemaker Partners</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -3036,47 +3067,47 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>海外（美国）</t>
+          <t>海外（新加坡）</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Zac Mohring</t>
+          <t>Paul Santos</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Principal（2026 年加入 AfterQuery 董事会）</t>
+          <t>Co-founder &amp; Managing Partner</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>未找到</t>
+          <t>官网 https://wavemaker.vc/ (搜索摘要；投递入口未在摘要中看到)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>When Altos led AfterQuery's Series A you called human data an enormous market and a critical bottleneck; we work with AfterQuery and build the trading environments alongside that data.</t>
+          <t>Wavemaker led ChemT's seed in June to bring AI to biomanufacturing; we apply the same thesis to finance, building RL environments and verifiers that make models useful to domain experts.</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>判断和我们完全一致，但 AfterQuery 是最直接的竞品，大概率不投；可以听反馈。</t>
+          <t>C 组（先发练手）：匹配度相对低，用这一组的回复打磨话术。</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Mohring 为 AfterQuery 董事，冲突最大，需先与 AfterQuery 沟通。</t>
+          <t>适配度偏弱：近期 AI 交易为生物制造，非 AI 数据/评测；东南亚区域限制。</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>https://www.businesswire.com/news/home/20260409469482/en/AfterQuery-Raises-$30-Million-Series-A-Round-at-$300-Million-Valuation (搜索摘要)</t>
+          <t>https://wavemaker.vc/chemt-biotechnology-raises-us5-million-bring-ai-to-biomanufacturing/ (搜索摘要) ; https://technode.global/2026/06/23/singapores-chemt-biotechnology-raises-4m-seed-round-to-build-ai-intelligence-layer-for-biomanufacturing/ (搜索摘要)</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>v-altos-ventures</t>
+          <t>v-wavemaker-partners</t>
         </is>
       </c>
     </row>
@@ -3086,32 +3117,32 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>C 组：先发练手</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Bessemer Venture Partners</t>
+          <t>字节跳动投资部</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>VC</t>
+          <t>战略投资</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>海外（美国）</t>
+          <t>海外（香港）</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Janelle Teng Wade</t>
+          <t>蒋恺</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Partner（负责 AI/ML、数据基础设施早期投资路线图）</t>
+          <t>香港财务投资团队负责人（前 Coatue 合伙人，2026-09 加入，向 CFO 高准汇报）</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -3121,27 +3152,27 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Your 2026 AI infrastructure roadmap flags RL-as-a-service as a frontier; we build the finance environments and verifiers those platforms need to train on.</t>
+          <t>看到您刚加入字节负责香港财务投资、系统布局 AI 初创；我们做金融方向的 RL 环境、验证器和专家数据，正在融种子轮。</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>种子轮投资（BVP 2026 年跟投了 Trajectory 种子轮）。</t>
+          <t>C 组（先发练手）：匹配度相对低，用这一组的回复打磨话术。</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>多阶段大基金，种子决策可能较慢。</t>
+          <t>字节自建专家平台；财务投资团队刚组建，种子轮是否在范围内未知。</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>https://www.bvp.com/news/bessemer-venture-partners-promotes-janelle-teng-to-partner (搜索摘要) ; https://www.bvp.com/atlas/ai-infrastructure-roadmap-five-frontiers-for-2026 (搜索摘要)</t>
+          <t>https://news.pedaily.cn/202609/569061.shtml（搜索摘要） ; https://news.qq.com/rain/a/20260911A0DZPW00（搜索摘要） ; https://www.sohu.com/a/1077273487_120088771（搜索摘要）</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>v-bessemer</t>
+          <t>v-bytedance-investment</t>
         </is>
       </c>
     </row>
@@ -3151,17 +3182,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>C 组：先发练手</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Exceptional Capital</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>VC</t>
+          <t>战略投资</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3171,42 +3202,34 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Marell Evans</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>创始人、General Partner</t>
-        </is>
-      </c>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>https://www.exceptionalcap.com（官网投递）</t>
+          <t>未找到</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Exceptional backed HUD at seed, where domain experts build RL environments for labs; we're building those environments for finance with our own expert network.</t>
+          <t>Datadog acquired Adaptive ML to bring RL post-training in-house for observability agents; we build RL environments and verifiers and could supply domain environments to that team.</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>种子轮跟投。</t>
+          <t>C 组（先发练手）：匹配度相对低，用这一组的回复打磨话术。 原排序理由：收购了 Adaptive ML，是后训练的买家和潜在退出方；战略沟通为主。</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>基金偏 B2B SaaS，单笔较小。</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.exceptionalcap.com/team/marell-evans (搜索摘要) ; https://en.wikipedia.org/wiki/Marell_Evans (搜索摘要)</t>
-        </is>
-      </c>
+          <t>作为投资人契合度弱；已投 Patronus。</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>v-exceptional-capital</t>
+          <t>v-datadog</t>
         </is>
       </c>
     </row>
@@ -3216,34 +3239,30 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>C 组：先发练手</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Ivan Burazin（Daytona CEO）</t>
+          <t>Emergence Capital</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>天使</t>
+          <t>VC</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>海外（美国/克罗地亚）</t>
+          <t>海外（美国）</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Ivan Burazin</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Co-founder &amp; CEO, Daytona</t>
-        </is>
-      </c>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
           <t>未找到</t>
@@ -3251,27 +3270,23 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>You angel-invested in HUD while RL and eval workloads grew to about half of Daytona's usage; we build the finance environments that would run in those sandboxes.</t>
+          <t>Emergence joined Arga's seed to give enterprise agents resettable practice environments; we build the same kind of environments for finance, from month-end close to trading.</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>天使投资；Daytona 亦可作为沙箱基础设施合作方。</t>
+          <t>C 组（先发练手）：匹配度相对低，用这一组的回复打磨话术。 原排序理由：投过企业软件 RL 沙箱，种子到 A 轮；据摘要是 Genspark 早期投资人（低置信度）。</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>无冲突。</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.daytona.io/dotfiles/author/ivan-burazin (搜索摘要) ; https://alleywatch.com/2026/02/daytona-ai-agent-infrastructure-sandbox-computing-developer-tools-ivan-burazin/ (搜索摘要)</t>
-        </is>
-      </c>
+          <t>Arga 负责人未公开；每位合伙人每年只投一家，门槛高。</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>v-ivan-burazin</t>
+          <t>v-emergence-capital</t>
         </is>
       </c>
     </row>
@@ -3281,12 +3296,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>C 组：先发练手</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Lightspeed</t>
+          <t>HKIC</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -3296,47 +3311,47 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>海外（美国）</t>
+          <t>海外（香港）</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Faraz Fatemi</t>
+          <t>未找到</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Partner（领投 Origin Lab 种子轮）</t>
+          <t>未找到</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>https://www.hkic.org.hk/contact-us（搜索摘要） ; 政府电话簿 https://tel.directory.gov.hk/HKIC_ENG.html（搜索摘要）</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>HKIC has made AI a core theme of its HK$62 billion mandate; we build finance RL environments and expert data and could anchor that work in Hong Kong.</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>C 组（先发练手）：匹配度相对低，用这一组的回复打磨话术。</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>政府引导型基金，要求香港落地；投资团队对接人未找到；称呼缺失，模板需用通用称呼。</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>未找到</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>You led Origin Lab's seed arguing frontier AI needs data grounded in interactive environments; financial markets are the interactive environment we build for.</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2026 年连续领投训练数据和评测的种子轮；投过 Pika，对华人团队友好。重要，但比第三批冲突少，放第二批末尾。</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>Fatemi 官网归类为 Consumer 合伙人，可能转给基础设施团队。</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>https://lsvp.com/team-member/faraz-fatemi/ (搜索摘要) ; https://www.businesswire.com/news/home/20260513129175/en/Origin-Lab-Raises-$8M-Seed-Led-by-Lightspeed-to-Build-the-Platform-Turning-Video-Game-Worlds-Into-Training-Data-for-AI (搜索摘要)</t>
-        </is>
-      </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>v-lightspeed</t>
+          <t>v-hkic</t>
         </is>
       </c>
     </row>
@@ -3346,62 +3361,54 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>C 组：先发练手</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Spiros Xanthos（Resolve AI CEO）</t>
+          <t>IMC Strategic Investments</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>天使</t>
+          <t>战略投资</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>海外（美国）</t>
+          <t>海外（荷兰/美国）</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Spiros Xanthos</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Founder &amp; CEO, Resolve AI</t>
-        </is>
-      </c>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>未找到</t>
+          <t>官网 Strategic Investments 页 https://www.imc.com/us/strategic-investments</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>You angel-invested in Bespoke Labs' seed and launched Resolve AI Labs for complex production environments; we build RL environments and verifiers, starting with finance and accounting.</t>
+          <t>IMC Strategic Investments backs trading infrastructure like Paradigm and McKay Brothers; we build AI training environments on market data, a new layer of that stack.</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>天使投资；Resolve AI Labs 亦为潜在环境客户。</t>
+          <t>C 组（先发练手）：匹配度相对低，用这一组的回复打磨话术。</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>无冲突。</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>https://resolve.ai/about-us (搜索摘要) ; https://www.crunchbase.com/person/spiros-xanthos-23ac (搜索摘要)</t>
-        </is>
-      </c>
+          <t>主投交易/市场基础设施，AI 训练数据契合度弱；负责人未找到。</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>v-spiros-xanthos</t>
+          <t>v-imc-strategic-investments</t>
         </is>
       </c>
     </row>
@@ -3411,17 +3418,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>C 组：先发练手</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Standard Capital</t>
+          <t>Nat Friedman &amp; Daniel Gross（NFDG / AI Grant）</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>VC</t>
+          <t>天使</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -3431,42 +3438,42 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Dalton Caldwell</t>
+          <t>Nat Friedman ; Daniel Gross</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>联合创始人、General Partner</t>
+          <t>Meta Superintelligence Labs</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>https://www.standardcap.com/apply（A 轮申请页）</t>
+          <t>未找到</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>You led HUD's Series A, where domain experts build RL environments and sell them to labs; we're building that for finance with our own expert network.</t>
+          <t>You backed Mechanize early, and Google has since brought its team into DeepMind; we're building RL environments for finance, the domain our founders traded in.</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>对 RL 环境有明确观点，但只做 A 轮；现在认识，为下一轮铺路。</t>
+          <t>C 组（先发练手）：匹配度相对低，用这一组的回复打磨话术。</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>只做 A 轮，种子不对口。</t>
+          <t>二人在 Meta，NFDG 被 Meta 部分收购，个人投资可及性低；AI Grant 2026 批次未确认。</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>https://www.standardcap.com/partners/dalton (搜索摘要) ; https://www.hud.ai/blog/announcing-16m-series-a (搜索摘要)</t>
+          <t>https://en.wikipedia.org/wiki/Nat_Friedman (搜索摘要) ; https://siliconangle.com/2025/07/03/safe-superintelligence-ceo-daniel-gross-joins-metas-new-ai-lab/ (搜索摘要)</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>v-standard-capital</t>
+          <t>v-nfdg</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3483,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>C 组：先发练手</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>The Raine Group</t>
+          <t>Openspace Ventures</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3491,47 +3498,47 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>海外（美国）</t>
+          <t>海外（新加坡）</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Landon Baker</t>
+          <t>Hian Goh</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Principal, Raine Ventures</t>
+          <t>Founding Partner</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>未找到</t>
+          <t>官网 https://www.openspacecapital.com/ (搜索摘要；投递入口未在摘要中看到)</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>You backed AfterQuery's Series A as expert data became critical to AI labs; we already work with AfterQuery and build the finance RL environments and verifiers alongside that data.</t>
+          <t>Openspace joined Eunice's $8M round this March for AI due diligence on alternative assets; we build the finance environments and verifiers used to train and test models for that kind of work.</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>商人银行背景，懂金融专家数据；但持有 AfterQuery。</t>
+          <t>C 组（先发练手）：匹配度相对低，用这一组的回复打磨话术。</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>投资 AfterQuery 的机构，提及合作前需创始人确认口径。</t>
+          <t>Eunice 由 Moonfire/Speedinvest 领投，Openspace 仅跟投；负责该交易的合伙人未找到；机构似已更名 Openspace Capital（多策略），早期仓位待确认。</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>https://raine.com/team/landon-baker/ (搜索摘要) ; https://www.businesswire.com/news/home/20260409469482/en/AfterQuery-Raises-$30-Million-Series-A-Round-at-$300-Million-Valuation (搜索摘要)</t>
+          <t>https://www.crunchbase.com/person/hian-goh/ (搜索摘要) ; https://www.kauffmanfellows.org/fellows/hian-goh (搜索摘要) ; https://www.openspacecapital.com/team (搜索摘要)</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>v-raine-group</t>
+          <t>v-openspace-ventures</t>
         </is>
       </c>
     </row>
@@ -3541,62 +3548,54 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>C 组：先发练手</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>A*</t>
+          <t>Samsung Next</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>VC</t>
+          <t>战略投资</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>海外（美国）</t>
+          <t>海外（韩国/美国）</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Kevin Hartz</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>联合创始人、General Partner</t>
-        </is>
-      </c>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>https://www.a-star.co（官网）</t>
+          <t>未找到</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>A* joined Index in Intelligence's $7.9M seed for AI evaluation; we build expert-scored environments for finance and are raising our seed now.</t>
+          <t>Samsung Next backed both Gray Swan and Patronus, two companies testing frontier models; we build the RL environments and verifiers used to train them, starting with finance.</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>种子轮领投或联合领投（甜区约 300 万美元，新募 4.5 亿美元基金）。</t>
+          <t>C 组（先发练手）：匹配度相对低，用这一组的回复打磨话术。 原排序理由：韩国战略方，连投两家评测公司，没有 RL 环境竞品。</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>负责 Intelligence 的合伙人未查到。</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>https://www.a-star.co/team (搜索摘要) ; https://www.bloomberg.com/news/articles/2026-05-12/vc-firm-takes-less-is-more-approach-with-new-450-million-fund (搜索摘要)</t>
-        </is>
-      </c>
+          <t>负责人未找到；Patronus 该轮有 SEC 备案质疑。</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>v-a-star</t>
+          <t>v-samsung-next</t>
         </is>
       </c>
     </row>
@@ -3606,34 +3605,30 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>C 组：先发练手</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Adam D'Angelo（Quora CEO）</t>
+          <t>Susquehanna International Group (SIG)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>天使</t>
+          <t>战略投资</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>海外（美国）</t>
+          <t>海外（美国，费城）</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Adam D'Angelo</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Founder &amp; CEO, Quora</t>
-        </is>
-      </c>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
           <t>未找到</t>
@@ -3641,27 +3636,27 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>You backed Mechanize's seed, and Google has since brought its RL environment team into DeepMind; we're building that category for finance and accounting.</t>
+          <t>Susquehanna backed Deccan AI's Series A in March for post-training data; we pair expert data with trading environments built by former quants.</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>背书型天使。</t>
+          <t>C 组（先发练手）：匹配度相对低，用这一组的回复打磨话术。 原排序理由：量化做市机构投过人类数据公司，背景相通；对接人需找。</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>可及性低；兼任 OpenAI 董事会成员（未在本轮单独核实）。</t>
+          <t>量化同业；投资负责人不明，Susquehanna Growth Equity 为成长期。</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Adam_D%27Angelo (搜索摘要) ; https://www.crunchbase.com/person/adam-dangelo (搜索摘要)</t>
+          <t>https://en.wikipedia.org/wiki/Susquehanna_International_Group (搜索摘要)</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>v-adam-dangelo</t>
+          <t>v-sig</t>
         </is>
       </c>
     </row>
@@ -3671,17 +3666,17 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>C 组：先发练手</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Alex Atallah（OpenRouter CEO）</t>
+          <t>Thrive Capital</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>天使</t>
+          <t>VC</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3691,42 +3686,38 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Alex Atallah</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Co-founder &amp; CEO, OpenRouter</t>
-        </is>
-      </c>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>个人主页 https://alexatallah.com/（无公开邮箱）</t>
+          <t>未找到</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>You backed Mechanize when RL environments were still a niche bet; we're building them for finance, with verifiers checked against real market data.</t>
+          <t>Thrive is reported to be leading Irregular's new round for testing frontier models in controlled environments; we build controlled environments for finance.</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>天使投资。</t>
+          <t>C 组（先发练手）：匹配度相对低，用这一组的回复打磨话术。</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>据报道 Stripe 2026-08 同意收购 OpenRouter，交割期精力有限。</t>
+          <t>阶段偏后，种子不对口；负责人不明。</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>https://ai.engineer/speakers/alex-atallah (搜索摘要) ; https://www.crunchbase.com/person/alex-atallah-912d (搜索摘要)</t>
+          <t>https://www.calcalistech.com/ctechnews/article/13p5khsib (搜索摘要)</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>v-alex-atallah</t>
+          <t>v-thrive-capital</t>
         </is>
       </c>
     </row>
@@ -3736,62 +3727,62 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>C 组：先发练手</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Antler Singapore</t>
+          <t>WorldQuant Ventures</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>加速器</t>
+          <t>VC</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>海外（新加坡）</t>
+          <t>海外（美国，康涅狄格）</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Jussi Salovaara</t>
+          <t>Steven Lau</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Co-founder, Antler; Managing Partner, Asia (Singapore-based)</t>
+          <t>Managing Partner</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Antler Singapore 官网申请 https://www.antler.co/location/singapore (搜索摘要；下一期驻留 2026-10-05 开始)</t>
+          <t>官网 https://www.worldquantventures.com/（第三方页面列出的通用邮箱未在官网核实，未采用）</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>You've said you'd rather back founders with deep domain expertise than new AI coding startups; we're four quants turning trading and accounting expertise into RL environments and verifiers for LLMs.</t>
+          <t>WorldQuant Ventures backs early-stage companies with a focus on data and finance; we're quants building RL environments and verifiers that train AI on financial tasks.</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>后续种子轮（Antler 对已成立团队可直投）或加入新加坡驻留计划。</t>
+          <t>C 组（先发练手）：匹配度相对低，用这一组的回复打磨话术。</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Antler 以 day-zero 驻留模式为主，已成型团队可能只适合其后续轮；新加坡团队层面对接人未找到。</t>
+          <t>联系人仅见第三方页面；近期投资偏航天/生物。</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>https://www.crunchbase.com/person/jussi-salovaara (搜索摘要) ; https://technode.global/2026/06/22/antler-showcases-28-startups-across-asia-building-autonomous-ai-systems-beyond-copilots/ (搜索摘要) ; https://sg.linkedin.com/in/jsalovaara (搜索摘要)</t>
+          <t>https://superscout.co/investor/worldquant-ventures (搜索摘要)</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>v-antler-singapore</t>
+          <t>v-worldquant-ventures</t>
         </is>
       </c>
     </row>
@@ -3801,62 +3792,58 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>C 组：先发练手</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Deviation Capital（原 Two Sigma Ventures）</t>
+          <t>Y Combinator</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>VC</t>
+          <t>加速器</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>海外（美国，纽约）</t>
+          <t>海外（美国）</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Colin Beirne</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Partner（Two Sigma Ventures 创始人）</t>
-        </is>
-      </c>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>未找到</t>
+          <t>https://www.ycombinator.com/rfs（RFS 页面，申请走 YC 官网）</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>You spun Deviation out of Two Sigma on a thesis of data science and computing upending industries; we're quants applying that to AI training, starting with finance RL environments.</t>
+          <t>YC's Requests for Startups ask for RL environments that train frontier models; we've built them for finance and already work with AfterQuery, a YC company.</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>种子/A 轮投资；量化背景天然认同。</t>
+          <t>C 组（先发练手）：匹配度相对低，用这一组的回复打磨话术。 原排序理由：本赛道孵化最多（AfterQuery、HUD、Halluminate、Datacurve 等），但批次内竞品多。</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-05 刚独立，投资节奏可能调整。</t>
+          <t>批次内竞品多（HUD、Halluminate 做金融服务 RL 环境等）；对已有团队价值主要在网络。</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>https://www.morningstar.com/news/business-wire/20260504832753/deviation-capital-launches-with-2b-aum-following-spinout-from-two-sigma (搜索摘要) ; https://pulse2.com/deviation-capital-launches-with-2-billion-in-aum-following-spinout-from-two-sigma/ (搜索摘要)</t>
+          <t>https://www.ycombinator.com/rfs (搜索摘要)</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>v-deviation-capital</t>
+          <t>v-y-combinator</t>
         </is>
       </c>
     </row>
@@ -3866,17 +3853,17 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>B 组</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Dheeraj Pandey（DevRev CEO）</t>
+          <t>Altos Ventures</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>天使</t>
+          <t>VC</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -3886,12 +3873,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Dheeraj Pandey</t>
+          <t>Zac Mohring</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Co-founder, CEO &amp; Chairman, DevRev</t>
+          <t>Principal（2026 年加入 AfterQuery 董事会）</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -3901,27 +3888,27 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>You angel-invested in Bespoke Labs' seed as RL environments for long-horizon agents took off; we build those environments for finance, from month-end close to trading.</t>
+          <t>When Altos led AfterQuery's Series A you called human data an enormous market and a critical bottleneck; we work with AfterQuery and build the trading environments alongside that data.</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>天使投资。</t>
+          <t>B 组：方向匹配，在 C 组之后发。 原排序理由：判断和我们完全一致，但 AfterQuery 是最直接的竞品，大概率不投；可以听反馈。</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>无冲突。</t>
+          <t>Mohring 为 AfterQuery 董事，冲突最大，需先与 AfterQuery 沟通。</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>https://devrev.ai/authors/dheeraj (搜索摘要) ; https://en.wikipedia.org/wiki/Dheeraj_Pandey (搜索摘要)</t>
+          <t>https://www.businesswire.com/news/home/20260409469482/en/AfterQuery-Raises-$30-Million-Series-A-Round-at-$300-Million-Valuation (搜索摘要)</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>v-dheeraj-pandey</t>
+          <t>v-altos-ventures</t>
         </is>
       </c>
     </row>
@@ -3931,62 +3918,62 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>B 组</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>DRW Venture Capital</t>
+          <t>Dylan Patel（SemiAnalysis）</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>VC</t>
+          <t>天使</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>海外（美国，芝加哥）</t>
+          <t>海外（美国）</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Kimberly Trautmann</t>
+          <t>Dylan Patel</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Partner &amp; Head of DRW Venture Capital</t>
+          <t>Founder, CEO &amp; Chief Analyst, SemiAnalysis</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>官网联系页 https://www.drw.com/contact-us</t>
+          <t>未找到</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>DRW VC backs fintech and enterprise tech where DRW's trading expertise adds value; we're ex-quants whose trading environment improved a 27B model's trading on unseen market data.</t>
+          <t>You angel-invested in HUD and co-wrote SemiAnalysis's piece on RL environments and data foundries; we're one of those foundries, focused on finance environments and verifiers.</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>种子/A 轮投资，单笔 $1M–5M+，无外部 LP，决策灵活。</t>
+          <t>B 组：方向匹配，在 C 组之后发。 原排序理由：活跃的 RL 基础设施天使，愿意投早期团队。</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>投资组合偏金融科技，AI 训练数据经验少。</t>
+          <t>无直接冲突；已投 HUD、Prime Intellect。</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>https://www.drw.com/vc (搜索摘要) ; https://www.rblt.com/fintech-summit-biography/kimberly-trautmann (搜索摘要)</t>
+          <t>https://semianalysis.com/dylan-patel/ (搜索摘要) ; https://www.hud.ai/blog/announcing-16m-series-a (搜索摘要)</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>v-drw-venture-capital</t>
+          <t>v-dylan-patel</t>
         </is>
       </c>
     </row>
@@ -3996,12 +3983,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>B 组</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Dwarkesh Patel</t>
+          <t>Ivan Burazin（Daytona CEO）</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4011,17 +3998,17 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>海外（美国）</t>
+          <t>海外（美国/克罗地亚）</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Dwarkesh Patel</t>
+          <t>Ivan Burazin</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Host, Dwarkesh Podcast</t>
+          <t>Co-founder &amp; CEO, Daytona</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -4031,27 +4018,27 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>You backed Mechanize and pressed Dario on why labs are building RL environments; we build them for finance, where rewards come from real market outcomes.</t>
+          <t>You angel-invested in HUD while RL and eval workloads grew to about half of Daytona's usage; we build the finance environments that would run in those sandboxes.</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>天使投资与播客曝光。</t>
+          <t>B 组：方向匹配，在 C 组之后发。</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>无公开联系渠道。</t>
+          <t>无冲突。</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Dwarkesh_Patel (搜索摘要) ; https://app.dealroom.co/companies/mechanize (搜索摘要)</t>
+          <t>https://www.daytona.io/dotfiles/author/ivan-burazin (搜索摘要) ; https://alleywatch.com/2026/02/daytona-ai-agent-infrastructure-sandbox-computing-developer-tools-ivan-burazin/ (搜索摘要)</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>v-dwarkesh-patel</t>
+          <t>v-ivan-burazin</t>
         </is>
       </c>
     </row>
@@ -4061,17 +4048,17 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>B 组</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>FPV Ventures</t>
+          <t>Spiros Xanthos（Resolve AI CEO）</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>VC</t>
+          <t>天使</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -4081,42 +4068,42 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Wesley Chan</t>
+          <t>Spiros Xanthos</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>联合创始人、Managing Partner</t>
+          <t>Founder &amp; CEO, Resolve AI</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>https://fpvventures.com/（官网）</t>
+          <t>未找到</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>FPV joined Origin Lab's seed for licensed AI training data; we build finance training data and RL environments with quant founders and our own experts.</t>
+          <t>You angel-invested in Bespoke Labs' seed and launched Resolve AI Labs for complex production environments; we build RL environments and verifiers, starting with finance and accounting.</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>种子轮投资。</t>
+          <t>B 组：方向匹配，在 C 组之后发。</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>负责 Origin Lab 的合伙人未确认。</t>
+          <t>无冲突。</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>https://fpvventures.com/team/ (搜索摘要) ; https://en.wikipedia.org/wiki/Wesley_Chan (搜索摘要)</t>
+          <t>https://resolve.ai/about-us (搜索摘要) ; https://www.crunchbase.com/person/spiros-xanthos-23ac (搜索摘要)</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>v-fpv-ventures</t>
+          <t>v-spiros-xanthos</t>
         </is>
       </c>
     </row>
@@ -4126,12 +4113,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>B 组</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Gobi Partners GBA (Alibaba Entrepreneurs Fund GP)</t>
+          <t>Standard Capital</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4141,47 +4128,47 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>海外（香港）</t>
+          <t>海外（美国）</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Chibo Tang</t>
+          <t>Dalton Caldwell</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Managing Partner, Gobi Partners (Gobi GBA; GP of Alibaba Hong Kong Entrepreneurs Fund)</t>
+          <t>联合创始人、General Partner</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>阿里巴巴香港创业者基金投资页 https://www.ent-fund.org/en/investment/hk (搜索摘要) ; https://www.gobi.vc/ (搜索摘要)</t>
+          <t>https://www.standardcap.com/apply（A 轮申请页）</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>You launched the Gobi–HKU Fund I in March to back AI spin-offs; we're Cambridge, LSE and Duke quants building finance RL environments and verifiers for LLM post-training, raising our seed.</t>
+          <t>You led HUD's Series A, where domain experts build RL environments and sell them to labs; we're building that for finance with our own expert network.</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>种子轮（AEF 香港基金投香港创始人/在港公司，AI 与金融科技为重点）。</t>
+          <t>B 组：方向匹配，在 C 组之后发。 原排序理由：对 RL 环境有明确观点，但只做 A 轮；现在认识，为下一轮铺路。</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>AEF 要求香港创始人或在港运营；Gobi–HKU 基金只投港大衍生项目；HKIC 为该基金出资方（HKIC 已在 V2 种子名单）。</t>
+          <t>只做 A 轮，种子不对口。</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>https://www.hku.hk/press/press-releases/detail/29006.html (搜索摘要) ; https://technode.global/2026/03/26/university-of-hong-kong-asia-focused-gobi-partners-launch-joint-fund-to-support-startups-innovations/ (搜索摘要)</t>
+          <t>https://www.standardcap.com/partners/dalton (搜索摘要) ; https://www.hud.ai/blog/announcing-16m-series-a (搜索摘要)</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>v-gobi-partners-gba</t>
+          <t>v-standard-capital</t>
         </is>
       </c>
     </row>
@@ -4191,17 +4178,17 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>B 组</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Gokul Rajaram</t>
+          <t>The Raine Group</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>天使</t>
+          <t>VC</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4211,12 +4198,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Gokul Rajaram</t>
+          <t>Landon Baker</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>天使投资人</t>
+          <t>Principal, Raine Ventures</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4226,27 +4213,27 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>You've backed Patronus from seed through its Series B as AI evaluation became infrastructure; we build the RL environments and verifiers on the training side, starting with finance.</t>
+          <t>You backed AfterQuery's Series A as expert data became critical to AI labs; we already work with AfterQuery and build the finance RL environments and verifiers alongside that data.</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>天使投资，常跟投种子轮。</t>
+          <t>B 组：方向匹配，在 C 组之后发。 原排序理由：商人银行背景，懂金融专家数据；但持有 AfterQuery。</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>当前全职职位未核实；Patronus 为相邻公司。</t>
+          <t>投资 AfterQuery 的机构，提及合作前需创始人确认口径。</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>https://www.patronus.ai/blog/patronus-launch (搜索摘要) ; https://www.prnewswire.com/news-releases/patronus-ai-raises-50-million-series-b-and-unveils-first-digital-world-models-for-ai-agent-training-and-simulation-302811248.html (搜索摘要)</t>
+          <t>https://raine.com/team/landon-baker/ (搜索摘要) ; https://www.businesswire.com/news/home/20260409469482/en/AfterQuery-Raises-$30-Million-Series-A-Round-at-$300-Million-Valuation (搜索摘要)</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>v-gokul-rajaram</t>
+          <t>v-raine-group</t>
         </is>
       </c>
     </row>
@@ -4256,12 +4243,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>B 组</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Golden Gate Ventures</t>
+          <t>776</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4271,47 +4258,47 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>海外（新加坡）</t>
+          <t>海外（美国）</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Vinnie Lauria</t>
+          <t>Alexis Ohanian</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Founding Partner</t>
+          <t>Founder</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>官网 https://www.goldengate.vc/ (搜索摘要；投递入口未在摘要中看到)</t>
+          <t>未找到</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>You led The Librarian's seed and called it one of the few AI launches that changes how people work; we build the finance RL environments and verifiers that make assistants reliable for professionals.</t>
+          <t>You led Deeptune's seed and then watched Mercor buy it for its RL environments; we're building that category for finance, with verifiers checked against real market data.</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>种子轮领投；另投过 AI 基础设施可观测性公司 Byanat（2025-02 Pre-A 领投）。</t>
+          <t>B 组：方向匹配，在 C 组之后发。 原排序理由：投过 RL 环境公司，且那家已被收购，组合里出现空位。</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>偏东南亚/中东应用层，AI 训练数据基础设施非其主赛道。</t>
+          <t>联系方式仅见第三方数据库，未写入。</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>https://www.goldengate.vc/team/vinnie-lauria (搜索摘要) ; https://technode.global/2025/11/14/the-librarian-raises-2m-in-seed-round-led-by-golden-gate-ventures/ (搜索摘要)</t>
+          <t>https://x.com/alexisohanian/status/2034760840562581881 (搜索摘要) ; https://en.wikipedia.org/wiki/Alexis_Ohanian (搜索摘要)</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>v-golden-gate-ventures</t>
+          <t>v-seven-seven-six</t>
         </is>
       </c>
     </row>
@@ -4321,12 +4308,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>B 组</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Granite Asia</t>
+          <t>A*</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4336,47 +4323,47 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>海外（新加坡）</t>
+          <t>海外（美国）</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Jenny Lee</t>
+          <t>Kevin Hartz</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Senior Managing Partner (Singapore; seed–Series A in AI, fintech, enterprise)</t>
+          <t>联合创始人、General Partner</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>官网 https://www.graniteasia.com/ (搜索摘要；投递入口未在摘要中看到)</t>
+          <t>https://www.a-star.co（官网）</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>You lead Granite Asia's seed-to-Series A investing across AI and fintech; we sit at that intersection, building finance RL environments, verifiers and expert data for LLM post-training.</t>
+          <t>A* joined Index in Intelligence's $7.9M seed for AI evaluation; we build expert-scored environments for finance and are raising our seed now.</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>种子轮（原 GGV 亚洲团队），并可借其 DBS 合作网络接触金融机构客户。</t>
+          <t>B 组：方向匹配，在 C 组之后发。</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Jenny Lee 为明星合伙人、冷邮件回复率低；2026 年重心含 AI IPO 基金与成长期；钩子较弱（岗位事实而非具体交易）。</t>
+          <t>负责 Intelligence 的合伙人未查到。</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>https://www.graniteasia.com/who-we-are?p=jenny-lee (搜索摘要) ; https://signal.nfx.com/investors/jenny-lee (搜索摘要) ; https://technode.global/2026/02/23/dbs-and-granite-asia-partner-to-launch-110m-ai-ipo-fund-for-asias-next-generation-companies/ (搜索摘要)</t>
+          <t>https://www.a-star.co/team (搜索摘要) ; https://www.bloomberg.com/news/articles/2026-05-12/vc-firm-takes-less-is-more-approach-with-new-450-million-fund (搜索摘要)</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>v-granite-asia</t>
+          <t>v-a-star</t>
         </is>
       </c>
     </row>
@@ -4386,12 +4373,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>B 组</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Greenfield Partners</t>
+          <t>Deviation Capital（原 Two Sigma Ventures）</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4401,17 +4388,17 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>海外（以色列/美国）</t>
+          <t>海外（美国，纽约）</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Itay Inbar</t>
+          <t>Colin Beirne</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>Partner（Two Sigma Ventures 创始人）</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4421,27 +4408,27 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>You led Patronus's Series B arguing simulations are becoming essential for AI to learn; we build simulation environments where outcomes settle in real markets, starting with trading.</t>
+          <t>You spun Deviation out of Two Sigma on a thesis of data science and computing upending industries; we're quants applying that to AI training, starting with finance RL environments.</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>观点吻合，可作为后续轮次或引荐方。</t>
+          <t>B 组：方向匹配，在 C 组之后发。</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>B 轮阶段；Patronus 为评测/仿真邻近公司；有媒体（The Dissent）质疑该轮缺少 SEC 备案。</t>
+          <t>2026-05 刚独立，投资节奏可能调整。</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/patronus-ai-raises-50-million-series-b-and-unveils-first-digital-world-models-for-ai-agent-training-and-simulation-302811248.html (搜索摘要) ; https://www.linkedin.com/in/itay-inbar-gp/ (搜索摘要)</t>
+          <t>https://www.morningstar.com/news/business-wire/20260504832753/deviation-capital-launches-with-2b-aum-following-spinout-from-two-sigma (搜索摘要) ; https://pulse2.com/deviation-capital-launches-with-2-billion-in-aum-following-spinout-from-two-sigma/ (搜索摘要)</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>v-greenfield-partners</t>
+          <t>v-deviation-capital</t>
         </is>
       </c>
     </row>
@@ -4451,12 +4438,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>B 组</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Homebrew</t>
+          <t>DRW Venture Capital</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4466,47 +4453,47 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>海外（美国）</t>
+          <t>海外（美国，芝加哥）</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Hunter Walk</t>
+          <t>Kimberly Trautmann</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>联合创始人、Partner</t>
+          <t>Partner &amp; Head of DRW Venture Capital</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>未找到</t>
+          <t>官网联系页 https://www.drw.com/contact-us</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Homebrew backed Datacurve's Series A for frontier coding data; we're doing the same for finance, with quant founders and our own expert network.</t>
+          <t>DRW VC backs fintech and enterprise tech where DRW's trading expertise adds value; we're ex-quants whose trading environment improved a 27B model's trading on unseen market data.</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>种子轮小额跟投。</t>
+          <t>B 组：方向匹配，在 C 组之后发。</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Homebrew 已不募外部资金，只用两位合伙人自有资金，单笔小。</t>
+          <t>投资组合偏金融科技，AI 训练数据经验少。</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>https://hunterwalk.com/about/ (搜索摘要) ; https://www.hustlefund.vc/post/how-hunter-walk-thinks-about-investments-and-what-early-stage-investors-can-learn (搜索摘要)</t>
+          <t>https://www.drw.com/vc (搜索摘要) ; https://www.rblt.com/fintech-summit-biography/kimberly-trautmann (搜索摘要)</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>v-homebrew</t>
+          <t>v-drw-venture-capital</t>
         </is>
       </c>
     </row>
@@ -4516,12 +4503,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>B 组</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Ian Livingstone（Keycard CEO）</t>
+          <t>Dwarkesh Patel</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -4536,12 +4523,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Ian Livingstone</t>
+          <t>Dwarkesh Patel</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Co-founder &amp; CEO, Keycard</t>
+          <t>Host, Dwarkesh Podcast</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -4551,27 +4538,27 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>You angel-invested in Veris AI's seed to train agents through simulated experience; we build that experience for finance agents, with verifiers checked against real market data.</t>
+          <t>You backed Mechanize and pressed Dario on why labs are building RL environments; we build them for finance, where rewards come from real market outcomes.</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>天使投资。</t>
+          <t>B 组：方向匹配，在 C 组之后发。</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>同名人物较多（另有游戏业 Ian Livingstone），发信前确认。</t>
+          <t>无公开联系渠道。</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>https://www.crunchbase.com/person/ian-livingstone-95d7 (搜索摘要) ; https://fintech.global/2025/10/23/keycard-secures-38m-to-advance-ai-agent-security/ (搜索摘要)</t>
+          <t>https://en.wikipedia.org/wiki/Dwarkesh_Patel (搜索摘要) ; https://app.dealroom.co/companies/mechanize (搜索摘要)</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>v-ian-livingstone</t>
+          <t>v-dwarkesh-patel</t>
         </is>
       </c>
     </row>
@@ -4581,62 +4568,62 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>B 组</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Iterative</t>
+          <t>Episode 1 Ventures</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>加速器</t>
+          <t>VC</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>海外（新加坡）</t>
+          <t>海外（英国，伦敦）</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Hsu Ken Ooi</t>
+          <t>Simon Murdoch</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder &amp; Managing Partner</t>
+          <t>Managing Partner</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>官网申请 https://www.iterative.vc/ (搜索摘要)；Office Hours 页 https://www.iterative.vc/post/office-hours-with-iterative-partners (搜索摘要)</t>
+          <t>官网 submit your deck 入口 https://www.episode1.com/</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Iterative co-led i10X's pre-seed in January 2026; we're quant founders building executable finance RL environments and verifiers for LLM post-training, and we're raising our seed.</t>
+          <t>You led Poindexter Labs' seed as it signed a frontier lab directly; we sell the same labs expert data and RL environments, built by Cambridge and LSE quants.</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>种子轮投资（10–50 万美元级）及东南亚落地支持。</t>
+          <t>B 组：方向匹配，在 C 组之后发。 原排序理由：欧洲少数领投 AI 训练数据种子轮的基金，竞争少、回复率可能更高。</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Iterative 只投东南亚相关公司，SimReal 需有新加坡实体或东南亚关联；票面较小。</t>
+          <t>已投 Poindexter（专家数据竞品）；Poindexter 由哪位合伙人负责未知。</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>https://www.iterative.vc/team (搜索摘要) ; https://hsukenooi.com/ (搜索摘要) ; https://www.crunchbase.com/person/hsu-ken-ooi (搜索摘要)</t>
+          <t>https://www.episode1.com/team (搜索摘要) ; https://www.crunchbase.com/person/simon-murdoch (搜索摘要)</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>v-iterative</t>
+          <t>v-episode-1</t>
         </is>
       </c>
     </row>
@@ -4646,12 +4633,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>B 组</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Jump Capital</t>
+          <t>FPV Ventures</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -4661,47 +4648,47 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>海外（美国，芝加哥）</t>
+          <t>海外（美国）</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Saaya Nath Pal</t>
+          <t>Wesley Chan</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>联合创始人、Managing Partner</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>官网联系表单（含 Funding 选项）https://jumpcap.com/contact/</t>
+          <t>https://fpvventures.com/（官网）</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Jump Capital just closed a $350M fund for AI infrastructure; we're ex-Jane Street and Citadel quants building RL environments for trading and finance, the picks and shovels of training.</t>
+          <t>FPV joined Origin Lab's seed for licensed AI training data; we build finance training data and RL environments with quant founders and our own experts.</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>种子轮投资；Jump Trading 背景与 Xitadel 高度相关。</t>
+          <t>B 组：方向匹配，在 C 组之后发。</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>主投 A 轮前后企业软件；哪位合伙人负责 AI 基础设施未明确。</t>
+          <t>负责 Origin Lab 的合伙人未确认。</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>https://jumpcap.com/insights/congratulations-to-our-new-partners-saaya-nath-and-tarun-gupta/ (搜索摘要) ; https://www.youtube.com/shorts/gggGy9Oq84c (搜索摘要)</t>
+          <t>https://fpvventures.com/team/ (搜索摘要) ; https://en.wikipedia.org/wiki/Wesley_Chan (搜索摘要)</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>v-jump-capital</t>
+          <t>v-fpv-ventures</t>
         </is>
       </c>
     </row>
@@ -4711,62 +4698,62 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>B 组</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Peak XV Partners (Surge)</t>
+          <t>Gokul Rajaram</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>加速器</t>
+          <t>天使</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>海外（新加坡）</t>
+          <t>海外（美国）</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Rajan Anandan</t>
+          <t>Gokul Rajaram</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Managing Director, Peak XV Partners; leads Surge (seed program)</t>
+          <t>天使投资人</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Surge 滚动申请页 https://surge.peakxv.com/ (搜索摘要；2026-09 新一期开营，官网 FAQ 称申请滚动开放 https://surge.peakxv.com/faqs)</t>
+          <t>未找到</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Surge 11 backed finance-AI teams like OnFinance and Finster; we build what sits upstream of such products: executable finance RL environments, verifiers and expert data, from a quant founding team.</t>
+          <t>You've backed Patronus from seed through its Series B as AI evaluation became infrastructure; we build the RL environments and verifiers on the training side, starting with finance.</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>申请 Surge 种子投资（最高 500 万美元），以金融 RL 环境+验证器+专家数据切入。</t>
+          <t>B 组：方向匹配，在 C 组之后发。</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Rajan 常驻德里、主看印度；Surge 以印度/东南亚为主，SimReal 若非新加坡/印度实体需说明区域相关性；2026-02 有合伙人离职。</t>
+          <t>当前全职职位未核实；Patronus 为相邻公司。</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>https://www.peakxv.com/team/rajan-anandan (搜索摘要) ; https://www.forbesindia.com/audio/forbes-india-tech-conver-sations/peak-xvs-shailendra-singh-rajan-anandan-open-up-on-their-dreams-for-surge/94447 (搜索摘要)</t>
+          <t>https://www.patronus.ai/blog/patronus-launch (搜索摘要) ; https://www.prnewswire.com/news-releases/patronus-ai-raises-50-million-series-b-and-unveils-first-digital-world-models-for-ai-agent-training-and-simulation-302811248.html (搜索摘要)</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>v-peak-xv-surge</t>
+          <t>v-gokul-rajaram</t>
         </is>
       </c>
     </row>
@@ -4776,12 +4763,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>B 组</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Point72 Ventures</t>
+          <t>Gradient Ventures</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -4796,42 +4783,42 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Sri Chandrasekar</t>
+          <t>Darian Shirazi</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Managing Partner</t>
+          <t>General Partner</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>官网联系页 https://p72.vc/contact/</t>
+          <t>未找到</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>You co-lead Point72 Ventures' AI investing and technical diligence; we're ex-Citadel and Millennium quants building RL environments that train AI agents on real market data.</t>
+          <t>Gradient joined Arga's seed for enterprise agent sandboxes and just closed a $220M seed fund; we're raising our seed to build RL environments for finance.</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>种子/A 轮投资；Point72 投研团队也是金融 AI 潜在客户。</t>
+          <t>B 组：方向匹配，在 C 组之后发。 原排序理由：Google 旗下种子基金，投过企业 RL 沙箱；Google 本身是 RL 环境大买家。</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>单笔 $5M–50M，偏大；钩子较泛（未找到其本赛道投资）。</t>
+          <t>Gradient 已从 Google 独立（Google 仍为 LP）；Arga 由哪位合伙人负责未知。</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>https://theorg.com/org/point72-ventures/org-chart/sri-chandrasekar (搜索摘要) ; https://signal.nfx.com/investors/sri-chandrasekar (搜索摘要)</t>
+          <t>https://www.businesswire.com/news/home/20260317890946/en/Gradient-Raises-$220M-Fifth-Fund-To-Seed-Next-Generation-of-AI-Founders (搜索摘要)</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>v-point72-ventures</t>
+          <t>v-gradient-ventures</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4828,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>B 组</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Redpoint</t>
+          <t>Homebrew</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -4861,12 +4848,12 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Jordan Segall</t>
+          <t>Hunter Walk</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>联合创始人、Partner</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -4876,27 +4863,27 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>You partnered with Irregular on its $80M round as frontier-lab evaluations became a real business; we sell frontier labs RL environments and verifiers, starting with finance.</t>
+          <t>Homebrew backed Datacurve's Series A for frontier coding data; we're doing the same for finance, with quant founders and our own expert network.</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>领投过前沿模型评测，没有竞品冲突。</t>
+          <t>B 组：方向匹配，在 C 组之后发。</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>Irregular 对接人身份主要来自 LinkedIn 摘要；无直接竞品冲突。</t>
+          <t>Homebrew 已不募外部资金，只用两位合伙人自有资金，单笔小。</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>https://www.redpoint.com/companies/irregular/ (搜索摘要) ; https://www.linkedin.com/posts/jordan-segall-7b938632_we-at-redpoint-are-so-proud-to-be-partnering-activity-7374144585985486848-XDPW (搜索摘要) ; https://signal.nfx.com/investors/jordan-segall (搜索摘要)</t>
+          <t>https://hunterwalk.com/about/ (搜索摘要) ; https://www.hustlefund.vc/post/how-hunter-walk-thinks-about-investments-and-what-early-stage-investors-can-learn (搜索摘要)</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>v-redpoint</t>
+          <t>v-homebrew</t>
         </is>
       </c>
     </row>
@@ -4906,12 +4893,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>B 组</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Sky9 Capital</t>
+          <t>Jump Capital</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -4921,47 +4908,47 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>海外（美国）</t>
+          <t>海外（美国，芝加哥）</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Ron Cao</t>
+          <t>Saaya Nath Pal</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Founding Partner</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>https://www.sky9capital.com/contact/（搜索摘要）</t>
+          <t>官网联系表单（含 Funding 选项）https://jumpcap.com/contact/</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>You led ProducerAI's seed in 2023 before Google acquired it; we're quant founders building executable finance RL environments, verifiers and expert data, and we're raising our seed.</t>
+          <t>Jump Capital just closed a $350M fund for AI infrastructure; we're ex-Jane Street and Citadel quants building RL environments for trading and finance, the picks and shovels of training.</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>美元种子轮投资，覆盖中美和新加坡。</t>
+          <t>B 组：方向匹配，在 C 组之后发。</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>对 RL 环境/数据赛道的认知未经证实；invest@sky9capital.com 据第三方说明只用于 LP 询问，未采用。</t>
+          <t>主投 A 轮前后企业软件；哪位合伙人负责 AI 基础设施未明确。</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>https://www.sky9capital.com/news/sky9-capital-portfolio-company-producerai-acquired-by-google/（搜索摘要） ; https://www.bloomberg.com/profile/person/16685992（搜索摘要） ; https://www.linkedin.com/in/sky9roncao/（搜索摘要）</t>
+          <t>https://jumpcap.com/insights/congratulations-to-our-new-partners-saaya-nath-and-tarun-gupta/ (搜索摘要) ; https://www.youtube.com/shorts/gggGy9Oq84c (搜索摘要)</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>v-sky9-capital</t>
+          <t>v-jump-capital</t>
         </is>
       </c>
     </row>
@@ -4971,12 +4958,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>B 组</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Valkyrie</t>
+          <t>Point72 Ventures</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -4991,42 +4978,42 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Beth Turner</t>
+          <t>Sri Chandrasekar</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>创始人、Solo GP（前 SV Angel 管理合伙人）</t>
+          <t>Managing Partner</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>https://www.valkyrie.vc/（官网）</t>
+          <t>官网联系页 https://p72.vc/contact/</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Valkyrie joined Intelligence's seed in August for human-preference evals; we build expert-scored finance environments, the next piece of that category.</t>
+          <t>You co-lead Point72 Ventures' AI investing and technical diligence; we're ex-Citadel and Millennium quants building RL environments that train AI agents on real market data.</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>种子轮跟投（4,500 万美元一期基金）。</t>
+          <t>B 组：方向匹配，在 C 组之后发。</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>单笔小；个人此前投过 Snorkel AI。</t>
+          <t>单笔 $5M–50M，偏大；钩子较泛（未找到其本赛道投资）。</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>https://www.forbes.com/sites/phoebeliu/2025/12/04/this-sv-angel-is-going-solo-with-a-45-million-venture-fund/ (搜索摘要) ; https://www.valkyrie.vc/ (搜索摘要)</t>
+          <t>https://theorg.com/org/point72-ventures/org-chart/sri-chandrasekar (搜索摘要) ; https://signal.nfx.com/investors/sri-chandrasekar (搜索摘要)</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>v-valkyrie</t>
+          <t>v-point72-ventures</t>
         </is>
       </c>
     </row>
@@ -5036,12 +5023,12 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>B 组</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Vanara Capital</t>
+          <t>Redpoint</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -5056,12 +5043,12 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Hayden Lekacz</t>
+          <t>Jordan Segall</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>联合创始人（Invisible 董事）</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -5071,27 +5058,27 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Vanara led Invisible's $100M round as a foundational layer of AI infrastructure; we're building that layer for finance, with quant founders and expert data.</t>
+          <t>You partnered with Irregular on its $80M round as frontier-lab evaluations became a real business; we sell frontier labs RL environments and verifiers, starting with finance.</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>后续轮次储备。</t>
+          <t>B 组：方向匹配，在 C 组之后发。 原排序理由：领投过前沿模型评测，没有竞品冲突。</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>成长期基金，2026 年未见新动作；Invisible 为专家数据竞品。</t>
+          <t>Irregular 对接人身份主要来自 LinkedIn 摘要；无直接竞品冲突。</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>https://www.businesswire.com/news/home/20250916425748/en/Invisible-Technologies-Raises-$100-Million-to-Power-the-Next-Generation-of-AI-Infrastructure-for-the-Enterprise (搜索摘要) ; https://www.eenewseurope.com/en/invisible-technologies-secures-100m-in-growth-funding-led-by-tpg-spinoff/ (搜索摘要)</t>
+          <t>https://www.redpoint.com/companies/irregular/ (搜索摘要) ; https://www.linkedin.com/posts/jordan-segall-7b938632_we-at-redpoint-are-so-proud-to-be-partnering-activity-7374144585985486848-XDPW (搜索摘要) ; https://signal.nfx.com/investors/jordan-segall (搜索摘要)</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>v-vanara-capital</t>
+          <t>v-redpoint</t>
         </is>
       </c>
     </row>
@@ -5101,12 +5088,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>B 组</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Vertex Ventures Southeast Asia &amp; India</t>
+          <t>Scribble Ventures</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -5116,47 +5103,47 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>海外（新加坡）</t>
+          <t>海外（美国）</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Jessica Koh</t>
+          <t>Stu Smith</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Senior Executive Director, Investment</t>
+          <t>Partner（发布 Proximal 领投帖）</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>https://www.vertexventures.sg/apply/（搜索摘要）</t>
+          <t>https://www.scribble.vc（官网 Contact 入口）</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>You led FORMAS.AI's pre-seed, noting AI is moving to integrated platforms with fine-tuning; we build finance RL environments and verifiers that feed that post-training loop.</t>
+          <t>Scribble led Proximal's round for long-horizon coding RL environments with fuzzy verifiers; we build the same kind of verified environments for trading and accounting.</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>美元种子轮，前提是设新加坡主体。</t>
+          <t>B 组：方向匹配，在 C 组之后发。 原排序理由：领投过 RL 环境公司的种子轮，单笔小（约 30 万–75 万美元）、决策快；Proximal 做编码，和金融不重叠。</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>聚焦东南亚和印度，需要新加坡主体；淡马锡本身以后期为主，未找到早期对接人（本行以 Vertex SEA&amp;I 代替）。</t>
+          <t>已投 Proximal（代码 RL 环境），方向不同但同赛道。</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>https://www.vertexventures.sg/news/formas-ai-raises-us-3-98-million-in-oversubscribed-pre-seed-round-to-build-the-ai-native-design-workspace-for-architecture/（搜索摘要） ; https://technode.global/2026/04/29/singapores-formas-ai-raises-3-98m-in-pre-seed-round-led-by-vertex-ventures-southeast-asia-india/（搜索摘要）</t>
+          <t>https://www.scribble.vc/stu (搜索摘要) ; https://www.linkedin.com/posts/imstusmith_excited-to-finally-share-that-scribble-ventures-activity-7430007099004432384-cqbR (搜索摘要)</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>v-vertex-ventures-sea</t>
+          <t>v-scribble-ventures</t>
         </is>
       </c>
     </row>
@@ -5166,12 +5153,12 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>B 组</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Wavemaker Partners</t>
+          <t>SV Angel</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -5181,47 +5168,47 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>海外（新加坡）</t>
+          <t>海外（美国）</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Paul Santos</t>
+          <t>Topher Conway</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Co-founder &amp; Managing Partner</t>
+          <t>Managing Partner</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>官网 https://wavemaker.vc/ (搜索摘要；投递入口未在摘要中看到)</t>
+          <t>未找到</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Wavemaker led ChemT's seed in June to bring AI to biomanufacturing; we apply the same thesis to finance, building RL environments and verifiers that make models useful to domain experts.</t>
+          <t>SV Angel is in the seed rounds of Arga and Origin Lab this year; we'd like to add a finance-focused RL environment company to that set.</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>种子轮（pre-seed 至 A 轮，企业软件/深科技方向）。</t>
+          <t>B 组：方向匹配，在 C 组之后发。 原排序理由：本赛道跟投最活跃的种子基金之一；投过 HeyGen，对华人团队友好。</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>适配度偏弱：近期 AI 交易为生物制造，非 AI 数据/评测；东南亚区域限制。</t>
+          <t>已投 Fleet；原种子基金负责人 Beth Turner 已离开创立 Valkyrie。</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>https://wavemaker.vc/chemt-biotechnology-raises-us5-million-bring-ai-to-biomanufacturing/ (搜索摘要) ; https://technode.global/2026/06/23/singapores-chemt-biotechnology-raises-4m-seed-round-to-build-ai-intelligence-layer-for-biomanufacturing/ (搜索摘要)</t>
+          <t>https://svangel.com/about/team (搜索摘要) ; https://www.crunchbase.com/person/topher-conway (搜索摘要)</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>v-wavemaker-partners</t>
+          <t>v-sv-angel</t>
         </is>
       </c>
     </row>
@@ -5231,62 +5218,62 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>B 组</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>字节跳动投资部</t>
+          <t>Valkyrie</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>战略投资</t>
+          <t>VC</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>海外（香港）</t>
+          <t>海外（美国）</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>蒋恺</t>
+          <t>Beth Turner</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>香港财务投资团队负责人（前 Coatue 合伙人，2026-09 加入，向 CFO 高准汇报）</t>
+          <t>创始人、Solo GP（前 SV Angel 管理合伙人）</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>未找到</t>
+          <t>https://www.valkyrie.vc/（官网）</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>看到您刚加入字节负责香港财务投资、系统布局 AI 初创；我们做金融方向的 RL 环境、验证器和专家数据，正在融种子轮。</t>
+          <t>Valkyrie joined Intelligence's seed in August for human-preference evals; we build expert-scored finance environments, the next piece of that category.</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>先做字节 Seed 的金融环境/专家数据供应商，再谈财务投资。</t>
+          <t>B 组：方向匹配，在 C 组之后发。</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>字节自建专家平台；财务投资团队刚组建，种子轮是否在范围内未知。</t>
+          <t>单笔小；个人此前投过 Snorkel AI。</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>https://news.pedaily.cn/202609/569061.shtml（搜索摘要） ; https://news.qq.com/rain/a/20260911A0DZPW00（搜索摘要） ; https://www.sohu.com/a/1077273487_120088771（搜索摘要）</t>
+          <t>https://www.forbes.com/sites/phoebeliu/2025/12/04/this-sv-angel-is-going-solo-with-a-45-million-venture-fund/ (搜索摘要) ; https://www.valkyrie.vc/ (搜索摘要)</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>v-bytedance-investment</t>
+          <t>v-valkyrie</t>
         </is>
       </c>
     </row>
@@ -5296,17 +5283,17 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>B 组</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>8VC</t>
+          <t>Yash Patil（Applied Compute CEO）</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>VC</t>
+          <t>天使</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -5316,38 +5303,42 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
+          <t>Yash Patil</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder &amp; CEO, Applied Compute</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
           <t>未找到</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>未找到</t>
-        </is>
-      </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>8VC led Bespoke Labs' seed before its $40M raise for agent training environments; we build those environments for finance.</t>
+          <t>You angel-invested in Deeptune while Applied Compute trains custom models for enterprises; we build finance and accounting RL environments that could feed those runs.</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>领投过 RL 环境种子轮，也是评测公司股东；持有 Bespoke。</t>
+          <t>B 组：方向匹配，在 C 组之后发。 原排序理由：天使投过 RL 环境；Applied Compute 同时是潜在客户，一次沟通两种机会。</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>已投 Bespoke Labs（RL 环境）构成冲突；负责合伙人不明。</t>
+          <t>Applied Compute 可能自建环境。</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>https://8vc.com/team (搜索摘要)</t>
+          <t>https://www.crunchbase.com/person/yash-patil-f81e (搜索摘要) ; https://www.forbes.com/sites/richardnieva/2026/09/01/applied-compute-openai-the-ex-openai-guys-building-cheaper-open-source-alternative/ (搜索摘要)</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>v-8vc</t>
+          <t>v-yash-patil</t>
         </is>
       </c>
     </row>
@@ -5357,17 +5348,17 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>B 组</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>BoxGroup</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>战略投资</t>
+          <t>VC</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -5377,34 +5368,42 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
+          <t>David Tisch</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
           <t>未找到</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>未找到</t>
-        </is>
-      </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Datadog acquired Adaptive ML to bring RL post-training in-house for observability agents; we build RL environments and verifiers and could supply domain environments to that team.</t>
+          <t>BoxGroup joined Arga's seed for enterprise agent sandboxes in August; we build the finance counterpart, with trading and month-end close environments.</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>收购了 Adaptive ML，是后训练的买家和潜在退出方；战略沟通为主。</t>
+          <t>B 组：方向匹配，在 C 组之后发。 原排序理由：早早投了两家金融背景团队做的 AI 数据/环境公司，看得懂我们的背景。</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>作为投资人契合度弱；已投 Patronus。</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr"/>
+          <t>同时是 AfterQuery 早期股东；负责 Arga 的合伙人不明。</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/BoxGroup (搜索摘要) ; https://theorg.com/org/boxgroup (搜索摘要)</t>
+        </is>
+      </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>v-datadog</t>
+          <t>v-boxgroup</t>
         </is>
       </c>
     </row>
@@ -5414,12 +5413,12 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>B 组</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>HKIC</t>
+          <t>Pear VC</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -5429,7 +5428,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>海外（香港）</t>
+          <t>海外（美国）</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -5437,39 +5436,31 @@
           <t>未找到</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>未找到</t>
-        </is>
-      </c>
+      <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>https://www.hkic.org.hk/contact-us（搜索摘要） ; 政府电话簿 https://tel.directory.gov.hk/HKIC_ENG.html（搜索摘要）</t>
+          <t>PearX 申请 https://pear.vc/pearx-application/ ；Pitch 页 https://www.pear.vc/pitch</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>HKIC has made AI a core theme of its HK$62 billion mandate; we build finance RL environments and expert data and could anchor that work in Hong Kong.</t>
+          <t>Pear backed Vals AI from seed through its a16z-led Series A as professional-task evals took off; we build RL environments and verifiers for finance tasks, one step past evaluation.</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>港元/美元投资，需在香港落地。</t>
+          <t>B 组：方向匹配，在 C 组之后发。 原排序理由：pre-seed/种子基金，评测公司股东，没有 RL 环境竞品。</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>政府引导型基金，要求香港落地；投资团队对接人未找到；称呼缺失，模板需用通用称呼。</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>未找到</t>
-        </is>
-      </c>
+          <t>负责 Vals 的合伙人未找到；Vals 在金融评测上与我们有重叠。</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>v-hkic</t>
+          <t>v-pear-vc</t>
         </is>
       </c>
     </row>
@@ -5479,22 +5470,22 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>B 组</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>IMC Strategic Investments</t>
+          <t>Sequoia Capital</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>战略投资</t>
+          <t>VC</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>海外（荷兰/美国）</t>
+          <t>海外（美国）</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -5505,28 +5496,32 @@
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>官网 Strategic Investments 页 https://www.imc.com/us/strategic-investments</t>
+          <t>未找到</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>IMC Strategic Investments backs trading infrastructure like Paradigm and McKay Brothers; we build AI training environments on market data, a new layer of that stack.</t>
+          <t>Sequoia has backed Fleet's enterprise RL environments since the seed; we go deeper on finance, with quant founders, expert data and trading environments scored by real markets.</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>战略投资；IMC 交易团队也可能是 Xitadel 客户。</t>
+          <t>B 组：方向匹配，在 C 组之后发。 原排序理由：多家 RL/评测公司股东，但持有 Fleet，负责人不明。</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>主投交易/市场基础设施，AI 训练数据契合度弱；负责人未找到。</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr"/>
+          <t>已投 Fleet（早期营收来自金融和保险客户的定制环境），直接竞争；负责合伙人不明。</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>https://sacra.com/c/fleet/ (搜索摘要)</t>
+        </is>
+      </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>v-imc-strategic-investments</t>
+          <t>v-sequoia</t>
         </is>
       </c>
     </row>
@@ -5536,17 +5531,17 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>A 组：最匹配，最后发</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Nat Friedman &amp; Daniel Gross（NFDG / AI Grant）</t>
+          <t>Acrew Capital</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>天使</t>
+          <t>VC</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -5556,12 +5551,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Nat Friedman ; Daniel Gross</t>
+          <t>Asad Khaliq</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Meta Superintelligence Labs</t>
+          <t>Founding Partner</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -5571,27 +5566,27 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>You backed Mechanize early, and Google has since brought its team into DeepMind; we're building RL environments for finance, the domain our founders traded in.</t>
+          <t>You co-led Veris AI's seed, backing agent training through experience rather than evaluation; we build that experience for finance agents, with verifiers checked against real market data.</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>更适合作为 Meta MSL 客户线索而非投资人。</t>
+          <t>A 组（最后发）：最匹配、最想拿下，话术成熟后再发。 原排序理由：同时投了模拟环境和专家数据两类公司，最容易听懂我们的定位；种子阶段对口。</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>二人在 Meta，NFDG 被 Meta 部分收购，个人投资可及性低；AI Grant 2026 批次未确认。</t>
+          <t>已投 Veris AI（相邻竞品）与 Invisible Technologies（专家数据竞品）。</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Nat_Friedman (搜索摘要) ; https://siliconangle.com/2025/07/03/safe-superintelligence-ceo-daniel-gross-joins-metas-new-ai-lab/ (搜索摘要)</t>
+          <t>https://www.acrewcapital.com/team-members/asad-khaliq (搜索摘要) ; https://www.crunchbase.com/person/asad-khaliq (搜索摘要)</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>v-nfdg</t>
+          <t>v-acrew-capital</t>
         </is>
       </c>
     </row>
@@ -5601,12 +5596,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>A 组：最匹配，最后发</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Openspace Ventures</t>
+          <t>Bessemer Venture Partners</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -5616,47 +5611,47 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>海外（新加坡）</t>
+          <t>海外（美国）</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Hian Goh</t>
+          <t>Janelle Teng Wade</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Founding Partner</t>
+          <t>Partner（负责 AI/ML、数据基础设施早期投资路线图）</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>官网 https://www.openspacecapital.com/ (搜索摘要；投递入口未在摘要中看到)</t>
+          <t>未找到</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Openspace joined Eunice's $8M round this March for AI due diligence on alternative assets; we build the finance environments and verifiers used to train and test models for that kind of work.</t>
+          <t>Your 2026 AI infrastructure roadmap flags RL-as-a-service as a frontier; we build the finance environments and verifiers those platforms need to train on.</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>种子轮跟投；金融 AI（投研/尽调）方向与其 Eunice 投资逻辑一致。</t>
+          <t>A 组（最后发）：最匹配、最想拿下，话术成熟后再发。</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>Eunice 由 Moonfire/Speedinvest 领投，Openspace 仅跟投；负责该交易的合伙人未找到；机构似已更名 Openspace Capital（多策略），早期仓位待确认。</t>
+          <t>多阶段大基金，种子决策可能较慢。</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>https://www.crunchbase.com/person/hian-goh/ (搜索摘要) ; https://www.kauffmanfellows.org/fellows/hian-goh (搜索摘要) ; https://www.openspacecapital.com/team (搜索摘要)</t>
+          <t>https://www.bvp.com/news/bessemer-venture-partners-promotes-janelle-teng-to-partner (搜索摘要) ; https://www.bvp.com/atlas/ai-infrastructure-roadmap-five-frontiers-for-2026 (搜索摘要)</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>v-openspace-ventures</t>
+          <t>v-bessemer</t>
         </is>
       </c>
     </row>
@@ -5666,54 +5661,62 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>A 组：最匹配，最后发</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Samsung Next</t>
+          <t>Decibel</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>战略投资</t>
+          <t>VC</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>海外（韩国/美国）</t>
+          <t>海外（美国）</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>未找到</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr"/>
+          <t>Alessio Fanelli</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Partner &amp; CTO</t>
+        </is>
+      </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>未找到</t>
+          <t>官网 Connect 页 https://www.decibel.vc/connect</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Samsung Next backed both Gray Swan and Patronus, two companies testing frontier models; we build the RL environments and verifiers used to train them, starting with finance.</t>
+          <t>You co-led Veris AI's seed as the environment layer enterprise AI was missing; we build that layer for finance, where agent outcomes settle against real markets.</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>韩国战略方，连投两家评测公司，没有 RL 环境竞品。</t>
+          <t>A 组（最后发）：最匹配、最想拿下，话术成熟后再发。 原排序理由：种子基金，领投过 agent 模拟环境；阶段完全对口。</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>负责人未找到；Patronus 该轮有 SEC 备案质疑。</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr"/>
+          <t>已投 Veris AI（企业 RL 环境，相邻竞品）。</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.decibel.vc/team/alessio-fanelli (搜索摘要) ; https://www.decibel.vc/articles/welcoming-alessio-fanelli-as-decibels-newest-partner (搜索摘要)</t>
+        </is>
+      </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>v-samsung-next</t>
+          <t>v-decibel</t>
         </is>
       </c>
     </row>
@@ -5723,12 +5726,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>A 组：最匹配，最后发</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Sequoia Capital</t>
+          <t>Exceptional Capital</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -5743,38 +5746,42 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>未找到</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr"/>
+          <t>Marell Evans</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>创始人、General Partner</t>
+        </is>
+      </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>未找到</t>
+          <t>https://www.exceptionalcap.com（官网投递）</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Sequoia has backed Fleet's enterprise RL environments since the seed; we go deeper on finance, with quant founders, expert data and trading environments scored by real markets.</t>
+          <t>Exceptional backed HUD at seed, where domain experts build RL environments for labs; we're building those environments for finance with our own expert network.</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>多家 RL/评测公司股东，但持有 Fleet，负责人不明。</t>
+          <t>A 组（最后发）：最匹配、最想拿下，话术成熟后再发。</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>已投 Fleet（早期营收来自金融和保险客户的定制环境），直接竞争；负责合伙人不明。</t>
+          <t>基金偏 B2B SaaS，单笔较小。</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>https://sacra.com/c/fleet/ (搜索摘要)</t>
+          <t>https://www.exceptionalcap.com/team/marell-evans (搜索摘要) ; https://en.wikipedia.org/wiki/Marell_Evans (搜索摘要)</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>v-sequoia</t>
+          <t>v-exceptional-capital</t>
         </is>
       </c>
     </row>
@@ -5784,58 +5791,62 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>A 组：最匹配，最后发</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Susquehanna International Group (SIG)</t>
+          <t>Kleiner Perkins</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>战略投资</t>
+          <t>VC</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>海外（美国，费城）</t>
+          <t>海外（美国）</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
+          <t>Leigh Marie Braswell</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Partner（主导 Applied Compute 投资）</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
           <t>未找到</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>未找到</t>
-        </is>
-      </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Susquehanna backed Deccan AI's Series A in March for post-training data; we pair expert data with trading environments built by former quants.</t>
+          <t>You backed Applied Compute on the view that enterprises lack the infrastructure to specialize models; we build the finance environments and verifiers those training runs need.</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>量化做市机构投过人类数据公司，背景相通；对接人需找。</t>
+          <t>A 组（最后发）：最匹配、最想拿下，话术成熟后再发。 原排序理由：合伙人懂数据业务；Applied Compute 是潜在客户，可形成组合协同。</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>量化同业；投资负责人不明，Susquehanna Growth Equity 为成长期。</t>
+          <t>Braswell 曾在 Scale AI 工作，可能以 Scale 标准审视数据质量。</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Susquehanna_International_Group (搜索摘要)</t>
+          <t>https://www.kleinerperkins.com/people/leigh-marie-braswell/ (搜索摘要) ; https://www.kleinerperkins.com/perspectives/applied-compute-closing-the-gap-between-frontier-ai-and-real-world-impact/ (搜索摘要)</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>v-sig</t>
+          <t>v-kleiner-perkins</t>
         </is>
       </c>
     </row>
@@ -5845,12 +5856,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>A 组：最匹配，最后发</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Thrive Capital</t>
+          <t>Lightspeed</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -5865,38 +5876,42 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
+          <t>Faraz Fatemi</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Partner（领投 Origin Lab 种子轮）</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
           <t>未找到</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>未找到</t>
-        </is>
-      </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Thrive is reported to be leading Irregular's new round for testing frontier models in controlled environments; we build controlled environments for finance.</t>
+          <t>You led Origin Lab's seed arguing frontier AI needs data grounded in interactive environments; financial markets are the interactive environment we build for.</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>后续轮次储备。</t>
+          <t>A 组（最后发）：最匹配、最想拿下，话术成熟后再发。 原排序理由：2026 年连续领投训练数据和评测的种子轮；投过 Pika，对华人团队友好。重要，但比第三批冲突少，放第二批末尾。</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>阶段偏后，种子不对口；负责人不明。</t>
+          <t>Fatemi 官网归类为 Consumer 合伙人，可能转给基础设施团队。</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>https://www.calcalistech.com/ctechnews/article/13p5khsib (搜索摘要)</t>
+          <t>https://lsvp.com/team-member/faraz-fatemi/ (搜索摘要) ; https://www.businesswire.com/news/home/20260513129175/en/Origin-Lab-Raises-$8M-Seed-Led-by-Lightspeed-to-Build-the-Platform-Turning-Video-Game-Worlds-Into-Training-Data-for-AI (搜索摘要)</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>v-thrive-capital</t>
+          <t>v-lightspeed</t>
         </is>
       </c>
     </row>
@@ -5906,12 +5921,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>A 组：最匹配，最后发</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>WorldQuant Ventures</t>
+          <t>Abstract Ventures</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -5921,47 +5936,47 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>海外（美国，康涅狄格）</t>
+          <t>海外（美国）</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Steven Lau</t>
+          <t>Ramtin Naimi</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Managing Partner</t>
+          <t>创始人、General Partner</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>官网 https://www.worldquantventures.com/（第三方页面列出的通用邮箱未在官网核实，未采用）</t>
+          <t>未找到</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>WorldQuant Ventures backs early-stage companies with a focus on data and finance; we're quants building RL environments and verifiers that train AI on financial tasks.</t>
+          <t>Abstract joined Deeptune's Series A for agent training gyms, accountant workflows included, before Mercor bought it; we build finance and month-end close environments in that category.</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>Pre-seed/种子/A 轮投资；WorldQuant 专家网络也可作供给来源。</t>
+          <t>A 组（最后发）：最匹配、最想拿下，话术成熟后再发。 原排序理由：RL 环境和后训练两边都跟投过；Deeptune 已并入 Mercor，竞品冲突减弱。</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>联系人仅见第三方页面；近期投资偏航天/生物。</t>
+          <t>无直接冲突。</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>https://superscout.co/investor/worldquant-ventures (搜索摘要)</t>
+          <t>https://www.crunchbase.com/person/ramtin-naimi (搜索摘要) ; https://signal.nfx.com/investors/ramtin-naimi (搜索摘要)</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>v-worldquant-ventures</t>
+          <t>v-abstract-ventures</t>
         </is>
       </c>
     </row>
@@ -5971,17 +5986,17 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>第 2 批</t>
+          <t>A 组：最匹配，最后发</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Y Combinator</t>
+          <t>Andreessen Horowitz (a16z)</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>加速器</t>
+          <t>VC</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -5991,38 +6006,42 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
+          <t>Martin Casado</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>General Partner（Infrastructure）</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
           <t>未找到</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ycombinator.com/rfs（RFS 页面，申请走 YC 官网）</t>
-        </is>
-      </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>YC's Requests for Startups ask for RL environments that train frontier models; we've built them for finance and already work with AfterQuery, a YC company.</t>
+          <t>Your Deeptune post argued the next decade of AI progress comes from better environments, not just better datasets; we build those environments for finance, scored by real markets.</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>本赛道孵化最多（AfterQuery、HUD、Halluminate、Datacurve 等），但批次内竞品多。</t>
+          <t>A 组（最后发）：最匹配、最想拿下，话术成熟后再发。 原排序理由：公开且明确的 RL 环境投资论点；Deeptune 被收购后留有空位；跟投过前 Citadel 团队的 Moment。</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>批次内竞品多（HUD、Halluminate 做金融服务 RL 环境等）；对已有团队价值主要在网络。</t>
+          <t>阶段偏 A 轮；已投 Vals、LMArena 等评测公司。</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>https://www.ycombinator.com/rfs (搜索摘要)</t>
+          <t>https://a16z.com/author/martin-casado/ (搜索摘要) ; https://a16z.com/podcast/jack-altman-martin-casado-on-the-future-of-vc/ (搜索摘要)</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>v-y-combinator</t>
+          <t>v-a16z</t>
         </is>
       </c>
     </row>
@@ -6032,12 +6051,12 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>第 3 批：最重要，话术熟了再发</t>
+          <t>A 组：最匹配，最后发</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Kleiner Perkins</t>
+          <t>Chemistry</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -6052,12 +6071,12 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Leigh Marie Braswell</t>
+          <t>Mark Goldberg</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Partner（主导 Applied Compute 投资）</t>
+          <t>Managing Partner、联合创始人</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -6067,27 +6086,27 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>You backed Applied Compute on the view that enterprises lack the infrastructure to specialize models; we build the finance environments and verifiers those training runs need.</t>
+          <t>You led Datacurve's Series A to take on Scale in coding data; we're building the finance equivalent, with quant experts and verifiable trading environments.</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>合伙人懂数据业务；Applied Compute 是潜在客户，可形成组合协同。</t>
+          <t>A 组（最后发）：最匹配、最想拿下，话术成熟后再发。 原排序理由：有 RL 投资论文，领投过年轻创始人的数据公司，对华人团队友好；持有 Datacurve（编码方向）。</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>Braswell 曾在 Scale AI 工作，可能以 Scale 标准审视数据质量。</t>
+          <t>Datacurve 若拓展金融数据则有重叠；Chemistry 正募 5 亿美元二期基金，窗口好。</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>https://www.kleinerperkins.com/people/leigh-marie-braswell/ (搜索摘要) ; https://www.kleinerperkins.com/perspectives/applied-compute-closing-the-gap-between-frontier-ai-and-real-world-impact/ (搜索摘要)</t>
+          <t>https://www.chemistry.vc/team/mark-goldberg (搜索摘要) ; https://techcrunch.com/2026/07/07/chemistry-ventures-is-raising-500m-for-its-second-fund/ (搜索摘要)</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>v-kleiner-perkins</t>
+          <t>v-chemistry</t>
         </is>
       </c>
     </row>
@@ -6097,17 +6116,17 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>第 3 批：最重要，话术熟了再发</t>
+          <t>A 组：最匹配，最后发</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Andreessen Horowitz (a16z)</t>
+          <t>Elad Gil</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>VC</t>
+          <t>天使</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -6117,12 +6136,12 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Martin Casado</t>
+          <t>Elad Gil</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>General Partner（Infrastructure）</t>
+          <t>个人投资人（2025 年起管理机构化基金）</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -6132,27 +6151,27 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Your Deeptune post argued the next decade of AI progress comes from better environments, not just better datasets; we build those environments for finance, scored by real markets.</t>
+          <t>You're reported to be in talks to lead Applied Compute's new round; as more companies train their own models with RL, they need domain environments, and we build them for finance.</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>公开且明确的 RL 环境投资论点；Deeptune 被收购后留有空位；跟投过前 Citadel 团队的 Moment。</t>
+          <t>A 组（最后发）：最匹配、最想拿下，话术成熟后再发。 原排序理由：信号型天使，后训练、评测、数据策展都投过；投过 HeyGen。</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>阶段偏 A 轮；已投 Vals、LMArena 等评测公司。</t>
+          <t>Applied Compute 轮次尚未确定；种子单笔可能较小，可及性低。</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>https://a16z.com/author/martin-casado/ (搜索摘要) ; https://a16z.com/podcast/jack-altman-martin-casado-on-the-future-of-vc/ (搜索摘要)</t>
+          <t>https://aiweekly.co/alerts/applied-compute-in-talks-for-3b-round-led-by-elad-gil (搜索摘要) ; https://www.thevccorner.com/p/elad-gil-solo-super-angel-solo-gp (搜索摘要)</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>v-a16z</t>
+          <t>v-elad-gil</t>
         </is>
       </c>
     </row>
@@ -6162,12 +6181,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>第 3 批：最重要，话术熟了再发</t>
+          <t>A 组：最匹配，最后发</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>8VC</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -6182,14 +6201,10 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Mark Goldberg</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>Managing Partner、联合创始人</t>
-        </is>
-      </c>
+          <t>未找到</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr">
         <is>
           <t>未找到</t>
@@ -6197,27 +6212,27 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>You led Datacurve's Series A to take on Scale in coding data; we're building the finance equivalent, with quant experts and verifiable trading environments.</t>
+          <t>8VC led Bespoke Labs' seed before its $40M raise for agent training environments; we build those environments for finance.</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>有 RL 投资论文，领投过年轻创始人的数据公司，对华人团队友好；持有 Datacurve（编码方向）。</t>
+          <t>A 组（最后发）：最匹配、最想拿下，话术成熟后再发。 原排序理由：领投过 RL 环境种子轮，也是评测公司股东；持有 Bespoke。</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>Datacurve 若拓展金融数据则有重叠；Chemistry 正募 5 亿美元二期基金，窗口好。</t>
+          <t>已投 Bespoke Labs（RL 环境）构成冲突；负责合伙人不明。</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>https://www.chemistry.vc/team/mark-goldberg (搜索摘要) ; https://techcrunch.com/2026/07/07/chemistry-ventures-is-raising-500m-for-its-second-fund/ (搜索摘要)</t>
+          <t>https://8vc.com/team (搜索摘要)</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>v-chemistry</t>
+          <t>v-8vc</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6242,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>第 3 批：最重要，话术熟了再发</t>
+          <t>A 组：最匹配，最后发</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -6263,7 +6278,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>唯一查到连续领投前 Citadel 量化团队的一线基金，也领投过后训练平台种子轮。</t>
+          <t>A 组（最后发）：最匹配、最想拿下，话术成熟后再发。 原排序理由：唯一查到连续领投前 Citadel 量化团队的一线基金，也领投过后训练平台种子轮。</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -6288,7 +6303,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>第 3 批：最重要，话术熟了再发</t>
+          <t>A 组：最匹配，最后发</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -6324,7 +6339,7 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>团队前东家之一，以机构名义领投过 AI 种子轮（Numerata），也是金融 RL 环境的潜在客户。</t>
+          <t>A 组（最后发）：最匹配、最想拿下，话术成熟后再发。 原排序理由：团队前东家之一，以机构名义领投过 AI 种子轮（Numerata），也是金融 RL 环境的潜在客户。</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -6697,7 +6712,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>批次：第 1 批是匹配度高、冲突小的种子基金和天使，先发，用回复打磨话术；第 3 批是最重要的几家，话术成熟后再发。</t>
+          <t>分组（Luke Sophinos 冷邮件方法）：按匹配度分 C / B / A 三组，从最不匹配的 C 组先发，用回复打磨话术和 BP；B 组其次；最匹配、最想拿下的 A 组最后发。</t>
         </is>
       </c>
     </row>
